--- a/Streamlit/Data/definitions.xlsx
+++ b/Streamlit/Data/definitions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4800" uniqueCount="1653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4802" uniqueCount="1655">
   <si>
     <t>Order</t>
   </si>
@@ -2432,6 +2432,9 @@
   </si>
   <si>
     <t>Rule-Based Methods</t>
+  </si>
+  <si>
+    <t>Chaos Theory</t>
   </si>
   <si>
     <t>S-shaped mathematical function that transforms unbounded input values into a bounded range, most commonly between 0 and 1, making it particularly useful in logistic regression, probability estimation, and neural networks. Bounding provides stability and diminishing sensitivity to extreme values, but this compression also reduces distinctions between very large or small inputs and can contribute to vanishing gradients in neural networks; while it may moderate the influence of extreme values. The logistic sigmoid originated from the logistic function developed by Belgian mathematician Pierre François Verhulst in the 1830s to model population growth. Its combination of nonlinearity, bounded output, and smooth transitions has made it an important function in statistical modeling and machine learning.</t>
@@ -4661,6 +4664,9 @@
   </si>
   <si>
     <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+  </si>
+  <si>
+    <t>Branch of mathematics, formally established in the 1960s, that studies complex dynamical systems highly sensitive to initial conditions. Its core principle—famously illustrated by the butterfly effect—demonstrates that minuscule shifts in a starting state can trigger vastly diverging outcomes over time. This framework is vital because it proves that fully deterministic systems can still generate fundamental unpredictability, shattering the traditional view of absolute clockwork order in nature. Today, its applications range from improving weather forecasting and analyzing economic market volatility to modeling complex biological rhythms.</t>
   </si>
   <si>
     <t>You do not specify the number of clusters in mean shift they are determined based on the density, it is most useful in applications of spatial hotspots, image segmentation, computer vision/object tracking, and exploratory clustering where the number of groups isn't known..</t>
@@ -5538,7 +5544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O863"/>
+  <dimension ref="A1:O864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -5635,7 +5641,7 @@
         <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -5674,7 +5680,7 @@
         <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -5688,7 +5694,7 @@
         <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -5702,7 +5708,7 @@
         <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -5716,7 +5722,7 @@
         <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -5730,7 +5736,7 @@
         <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -5744,7 +5750,7 @@
         <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -5772,7 +5778,7 @@
         <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="K15" t="s">
         <v>595</v>
@@ -5787,7 +5793,7 @@
         <v>90</v>
       </c>
       <c r="O15" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -5801,7 +5807,7 @@
         <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="K16" t="s">
         <v>596</v>
@@ -5816,7 +5822,7 @@
         <v>91</v>
       </c>
       <c r="O16" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="17" spans="2:15">
@@ -5830,7 +5836,7 @@
         <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="K17" t="s">
         <v>595</v>
@@ -5859,7 +5865,7 @@
         <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K18" t="s">
         <v>595</v>
@@ -5888,16 +5894,16 @@
         <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K19" t="s">
         <v>596</v>
       </c>
       <c r="L19" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="M19" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="N19" t="s">
         <v>94</v>
@@ -5917,7 +5923,7 @@
         <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="K20" t="s">
         <v>595</v>
@@ -5946,7 +5952,7 @@
         <v>96</v>
       </c>
       <c r="E21" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K21" t="s">
         <v>596</v>
@@ -5955,7 +5961,7 @@
         <v>592</v>
       </c>
       <c r="M21" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N21" t="s">
         <v>96</v>
@@ -5975,22 +5981,22 @@
         <v>97</v>
       </c>
       <c r="E22" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="K22" t="s">
         <v>595</v>
       </c>
       <c r="L22" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="M22" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="N22" t="s">
         <v>97</v>
       </c>
       <c r="O22" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="23" spans="2:15">
@@ -6004,7 +6010,7 @@
         <v>98</v>
       </c>
       <c r="E23" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K23" t="s">
         <v>595</v>
@@ -6033,7 +6039,7 @@
         <v>99</v>
       </c>
       <c r="E24" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K24" t="s">
         <v>595</v>
@@ -6042,13 +6048,13 @@
         <v>584</v>
       </c>
       <c r="M24" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="N24" t="s">
         <v>99</v>
       </c>
       <c r="O24" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="25" spans="2:15">
@@ -6062,7 +6068,7 @@
         <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K25" t="s">
         <v>596</v>
@@ -6071,13 +6077,13 @@
         <v>588</v>
       </c>
       <c r="M25" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N25" t="s">
         <v>100</v>
       </c>
       <c r="O25" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="26" spans="2:15">
@@ -6091,7 +6097,7 @@
         <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="K26" t="s">
         <v>595</v>
@@ -6106,7 +6112,7 @@
         <v>101</v>
       </c>
       <c r="O26" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="27" spans="2:15">
@@ -6120,7 +6126,7 @@
         <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="K27" t="s">
         <v>595</v>
@@ -6149,7 +6155,7 @@
         <v>103</v>
       </c>
       <c r="E28" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="K28" t="s">
         <v>596</v>
@@ -6164,7 +6170,7 @@
         <v>103</v>
       </c>
       <c r="O28" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="29" spans="2:15">
@@ -6178,7 +6184,7 @@
         <v>104</v>
       </c>
       <c r="E29" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="K29" t="s">
         <v>595</v>
@@ -6193,7 +6199,7 @@
         <v>104</v>
       </c>
       <c r="O29" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="30" spans="2:15">
@@ -6207,7 +6213,7 @@
         <v>105</v>
       </c>
       <c r="E30" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="K30" t="s">
         <v>595</v>
@@ -6222,7 +6228,7 @@
         <v>105</v>
       </c>
       <c r="O30" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="31" spans="2:15">
@@ -6236,7 +6242,7 @@
         <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="K31" t="s">
         <v>596</v>
@@ -6265,7 +6271,7 @@
         <v>107</v>
       </c>
       <c r="E32" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K32" t="s">
         <v>596</v>
@@ -6274,13 +6280,13 @@
         <v>588</v>
       </c>
       <c r="M32" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N32" t="s">
         <v>107</v>
       </c>
       <c r="O32" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="33" spans="2:15">
@@ -6294,7 +6300,7 @@
         <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K33" t="s">
         <v>595</v>
@@ -6323,7 +6329,7 @@
         <v>109</v>
       </c>
       <c r="E34" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K34" t="s">
         <v>595</v>
@@ -6332,7 +6338,7 @@
         <v>585</v>
       </c>
       <c r="M34" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N34" t="s">
         <v>109</v>
@@ -6352,7 +6358,7 @@
         <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K35" t="s">
         <v>596</v>
@@ -6367,7 +6373,7 @@
         <v>110</v>
       </c>
       <c r="O35" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="36" spans="2:15">
@@ -6381,7 +6387,7 @@
         <v>111</v>
       </c>
       <c r="E36" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="K36" t="s">
         <v>595</v>
@@ -6396,7 +6402,7 @@
         <v>111</v>
       </c>
       <c r="O36" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="37" spans="2:15">
@@ -6410,7 +6416,7 @@
         <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="K37" t="s">
         <v>595</v>
@@ -6425,7 +6431,7 @@
         <v>112</v>
       </c>
       <c r="O37" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="38" spans="2:15">
@@ -6439,7 +6445,7 @@
         <v>113</v>
       </c>
       <c r="E38" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K38" t="s">
         <v>595</v>
@@ -6448,13 +6454,13 @@
         <v>585</v>
       </c>
       <c r="M38" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N38" t="s">
         <v>113</v>
       </c>
       <c r="O38" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="39" spans="2:15">
@@ -6468,7 +6474,7 @@
         <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="K39" t="s">
         <v>596</v>
@@ -6477,7 +6483,7 @@
         <v>588</v>
       </c>
       <c r="M39" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="N39" t="s">
         <v>114</v>
@@ -6497,7 +6503,7 @@
         <v>115</v>
       </c>
       <c r="E40" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="K40" t="s">
         <v>596</v>
@@ -6506,7 +6512,7 @@
         <v>588</v>
       </c>
       <c r="M40" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="N40" t="s">
         <v>115</v>
@@ -6526,7 +6532,7 @@
         <v>116</v>
       </c>
       <c r="E41" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K41" t="s">
         <v>596</v>
@@ -6535,7 +6541,7 @@
         <v>588</v>
       </c>
       <c r="M41" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="N41" t="s">
         <v>116</v>
@@ -6555,7 +6561,7 @@
         <v>117</v>
       </c>
       <c r="E42" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K42" t="s">
         <v>596</v>
@@ -6564,7 +6570,7 @@
         <v>589</v>
       </c>
       <c r="M42" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="N42" t="s">
         <v>117</v>
@@ -6584,7 +6590,7 @@
         <v>118</v>
       </c>
       <c r="E43" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="K43" t="s">
         <v>595</v>
@@ -6593,13 +6599,13 @@
         <v>589</v>
       </c>
       <c r="M43" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="N43" t="s">
         <v>118</v>
       </c>
       <c r="O43" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -6613,7 +6619,7 @@
         <v>119</v>
       </c>
       <c r="E44" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="K44" t="s">
         <v>595</v>
@@ -6628,7 +6634,7 @@
         <v>119</v>
       </c>
       <c r="O44" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -6642,7 +6648,7 @@
         <v>120</v>
       </c>
       <c r="E45" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="K45" t="s">
         <v>595</v>
@@ -6657,7 +6663,7 @@
         <v>120</v>
       </c>
       <c r="O45" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -6671,7 +6677,7 @@
         <v>121</v>
       </c>
       <c r="E46" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K46" t="s">
         <v>595</v>
@@ -6680,13 +6686,13 @@
         <v>585</v>
       </c>
       <c r="M46" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N46" t="s">
         <v>121</v>
       </c>
       <c r="O46" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -6700,7 +6706,7 @@
         <v>122</v>
       </c>
       <c r="E47" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="K47" t="s">
         <v>596</v>
@@ -6709,13 +6715,13 @@
         <v>20</v>
       </c>
       <c r="M47" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="N47" t="s">
         <v>122</v>
       </c>
       <c r="O47" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -6729,7 +6735,7 @@
         <v>123</v>
       </c>
       <c r="E48" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="K48" t="s">
         <v>595</v>
@@ -6738,7 +6744,7 @@
         <v>584</v>
       </c>
       <c r="M48" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="N48" t="s">
         <v>123</v>
@@ -6758,7 +6764,7 @@
         <v>124</v>
       </c>
       <c r="E49" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="K49" t="s">
         <v>595</v>
@@ -6767,7 +6773,7 @@
         <v>585</v>
       </c>
       <c r="M49" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N49" t="s">
         <v>124</v>
@@ -6787,7 +6793,7 @@
         <v>125</v>
       </c>
       <c r="E50" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="K50" t="s">
         <v>596</v>
@@ -6796,7 +6802,7 @@
         <v>588</v>
       </c>
       <c r="M50" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N50" t="s">
         <v>125</v>
@@ -6816,7 +6822,7 @@
         <v>126</v>
       </c>
       <c r="E51" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K51" t="s">
         <v>595</v>
@@ -6825,13 +6831,13 @@
         <v>585</v>
       </c>
       <c r="M51" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N51" t="s">
         <v>126</v>
       </c>
       <c r="O51" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="52" spans="2:15">
@@ -6845,7 +6851,7 @@
         <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="K52" t="s">
         <v>595</v>
@@ -6860,7 +6866,7 @@
         <v>127</v>
       </c>
       <c r="O52" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="53" spans="2:15">
@@ -6874,7 +6880,7 @@
         <v>128</v>
       </c>
       <c r="E53" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="K53" t="s">
         <v>595</v>
@@ -6883,13 +6889,13 @@
         <v>585</v>
       </c>
       <c r="M53" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="N53" t="s">
         <v>128</v>
       </c>
       <c r="O53" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="54" spans="2:15">
@@ -6903,7 +6909,7 @@
         <v>129</v>
       </c>
       <c r="E54" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K54" t="s">
         <v>596</v>
@@ -6912,13 +6918,13 @@
         <v>589</v>
       </c>
       <c r="M54" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="N54" t="s">
         <v>129</v>
       </c>
       <c r="O54" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="55" spans="2:15">
@@ -6932,7 +6938,7 @@
         <v>130</v>
       </c>
       <c r="E55" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="K55" t="s">
         <v>595</v>
@@ -6941,13 +6947,13 @@
         <v>589</v>
       </c>
       <c r="M55" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N55" t="s">
         <v>130</v>
       </c>
       <c r="O55" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="56" spans="2:15">
@@ -6961,7 +6967,7 @@
         <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="K56" t="s">
         <v>596</v>
@@ -6970,13 +6976,13 @@
         <v>588</v>
       </c>
       <c r="M56" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="N56" t="s">
         <v>131</v>
       </c>
       <c r="O56" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="57" spans="2:15">
@@ -6990,7 +6996,7 @@
         <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K57" t="s">
         <v>595</v>
@@ -6999,13 +7005,13 @@
         <v>584</v>
       </c>
       <c r="M57" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="N57" t="s">
         <v>132</v>
       </c>
       <c r="O57" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="58" spans="2:15">
@@ -7019,7 +7025,7 @@
         <v>133</v>
       </c>
       <c r="E58" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="K58" t="s">
         <v>595</v>
@@ -7028,7 +7034,7 @@
         <v>585</v>
       </c>
       <c r="M58" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="N58" t="s">
         <v>133</v>
@@ -7048,7 +7054,7 @@
         <v>134</v>
       </c>
       <c r="E59" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K59" t="s">
         <v>596</v>
@@ -7063,7 +7069,7 @@
         <v>134</v>
       </c>
       <c r="O59" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="60" spans="2:15">
@@ -7077,7 +7083,7 @@
         <v>135</v>
       </c>
       <c r="E60" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K60" t="s">
         <v>596</v>
@@ -7086,7 +7092,7 @@
         <v>588</v>
       </c>
       <c r="M60" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="N60" t="s">
         <v>135</v>
@@ -7106,7 +7112,7 @@
         <v>136</v>
       </c>
       <c r="E61" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="K61" t="s">
         <v>595</v>
@@ -7115,13 +7121,13 @@
         <v>585</v>
       </c>
       <c r="M61" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N61" t="s">
         <v>136</v>
       </c>
       <c r="O61" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="62" spans="2:15">
@@ -7135,7 +7141,7 @@
         <v>137</v>
       </c>
       <c r="E62" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="K62" t="s">
         <v>596</v>
@@ -7144,13 +7150,13 @@
         <v>588</v>
       </c>
       <c r="M62" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="N62" t="s">
         <v>137</v>
       </c>
       <c r="O62" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="63" spans="2:15">
@@ -7164,7 +7170,7 @@
         <v>138</v>
       </c>
       <c r="E63" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="K63" t="s">
         <v>596</v>
@@ -7173,13 +7179,13 @@
         <v>587</v>
       </c>
       <c r="M63" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="N63" t="s">
         <v>138</v>
       </c>
       <c r="O63" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="64" spans="2:15">
@@ -7193,7 +7199,7 @@
         <v>139</v>
       </c>
       <c r="E64" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="K64" t="s">
         <v>596</v>
@@ -7208,7 +7214,7 @@
         <v>139</v>
       </c>
       <c r="O64" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="65" spans="2:15">
@@ -7222,7 +7228,7 @@
         <v>140</v>
       </c>
       <c r="E65" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="K65" t="s">
         <v>595</v>
@@ -7231,7 +7237,7 @@
         <v>585</v>
       </c>
       <c r="M65" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="N65" t="s">
         <v>140</v>
@@ -7251,7 +7257,7 @@
         <v>141</v>
       </c>
       <c r="E66" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K66" t="s">
         <v>595</v>
@@ -7260,13 +7266,13 @@
         <v>585</v>
       </c>
       <c r="M66" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="N66" t="s">
         <v>141</v>
       </c>
       <c r="O66" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="67" spans="2:15">
@@ -7280,13 +7286,13 @@
         <v>142</v>
       </c>
       <c r="E67" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="K67" t="s">
         <v>596</v>
       </c>
       <c r="L67" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="M67" t="s">
         <v>443</v>
@@ -7295,7 +7301,7 @@
         <v>142</v>
       </c>
       <c r="O67" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="68" spans="2:15">
@@ -7309,7 +7315,7 @@
         <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="K68" t="s">
         <v>595</v>
@@ -7338,7 +7344,7 @@
         <v>144</v>
       </c>
       <c r="E69" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="K69" t="s">
         <v>595</v>
@@ -7347,7 +7353,7 @@
         <v>585</v>
       </c>
       <c r="M69" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="N69" t="s">
         <v>144</v>
@@ -7367,7 +7373,7 @@
         <v>145</v>
       </c>
       <c r="E70" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="K70" t="s">
         <v>595</v>
@@ -7376,13 +7382,13 @@
         <v>585</v>
       </c>
       <c r="M70" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="N70" t="s">
         <v>145</v>
       </c>
       <c r="O70" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="71" spans="2:15">
@@ -7396,7 +7402,7 @@
         <v>146</v>
       </c>
       <c r="E71" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="K71" t="s">
         <v>595</v>
@@ -7425,7 +7431,7 @@
         <v>147</v>
       </c>
       <c r="E72" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="K72" t="s">
         <v>595</v>
@@ -7454,7 +7460,7 @@
         <v>148</v>
       </c>
       <c r="E73" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="K73" t="s">
         <v>596</v>
@@ -7463,7 +7469,7 @@
         <v>588</v>
       </c>
       <c r="M73" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="N73" t="s">
         <v>148</v>
@@ -7483,7 +7489,7 @@
         <v>149</v>
       </c>
       <c r="E74" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="K74" t="s">
         <v>595</v>
@@ -7492,13 +7498,13 @@
         <v>585</v>
       </c>
       <c r="M74" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="N74" t="s">
         <v>149</v>
       </c>
       <c r="O74" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="75" spans="2:15">
@@ -7512,7 +7518,7 @@
         <v>150</v>
       </c>
       <c r="E75" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="K75" t="s">
         <v>596</v>
@@ -7521,7 +7527,7 @@
         <v>583</v>
       </c>
       <c r="M75" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="N75" t="s">
         <v>150</v>
@@ -7541,7 +7547,7 @@
         <v>151</v>
       </c>
       <c r="E76" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K76" t="s">
         <v>595</v>
@@ -7550,13 +7556,13 @@
         <v>584</v>
       </c>
       <c r="M76" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N76" t="s">
         <v>151</v>
       </c>
       <c r="O76" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="77" spans="2:15">
@@ -7570,7 +7576,7 @@
         <v>152</v>
       </c>
       <c r="E77" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="K77" t="s">
         <v>596</v>
@@ -7579,7 +7585,7 @@
         <v>588</v>
       </c>
       <c r="M77" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="N77" t="s">
         <v>152</v>
@@ -7599,7 +7605,7 @@
         <v>153</v>
       </c>
       <c r="E78" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="K78" t="s">
         <v>596</v>
@@ -7608,13 +7614,13 @@
         <v>583</v>
       </c>
       <c r="M78" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="N78" t="s">
         <v>153</v>
       </c>
       <c r="O78" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="79" spans="2:15">
@@ -7628,7 +7634,7 @@
         <v>154</v>
       </c>
       <c r="E79" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="K79" t="s">
         <v>596</v>
@@ -7657,7 +7663,7 @@
         <v>155</v>
       </c>
       <c r="E80" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K80" t="s">
         <v>596</v>
@@ -7672,7 +7678,7 @@
         <v>155</v>
       </c>
       <c r="O80" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="81" spans="2:15">
@@ -7686,7 +7692,7 @@
         <v>156</v>
       </c>
       <c r="E81" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="K81" t="s">
         <v>596</v>
@@ -7695,7 +7701,7 @@
         <v>588</v>
       </c>
       <c r="M81" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N81" t="s">
         <v>156</v>
@@ -7715,7 +7721,7 @@
         <v>157</v>
       </c>
       <c r="E82" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="K82" t="s">
         <v>595</v>
@@ -7744,7 +7750,7 @@
         <v>158</v>
       </c>
       <c r="E83" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="K83" t="s">
         <v>595</v>
@@ -7759,7 +7765,7 @@
         <v>158</v>
       </c>
       <c r="O83" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="84" spans="2:15">
@@ -7773,7 +7779,7 @@
         <v>159</v>
       </c>
       <c r="E84" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="K84" t="s">
         <v>595</v>
@@ -7788,7 +7794,7 @@
         <v>159</v>
       </c>
       <c r="O84" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="85" spans="2:15">
@@ -7802,7 +7808,7 @@
         <v>160</v>
       </c>
       <c r="E85" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="K85" t="s">
         <v>595</v>
@@ -7811,7 +7817,7 @@
         <v>585</v>
       </c>
       <c r="M85" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N85" t="s">
         <v>160</v>
@@ -7831,7 +7837,7 @@
         <v>161</v>
       </c>
       <c r="E86" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="K86" t="s">
         <v>595</v>
@@ -7840,7 +7846,7 @@
         <v>585</v>
       </c>
       <c r="M86" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="N86" t="s">
         <v>161</v>
@@ -7860,7 +7866,7 @@
         <v>162</v>
       </c>
       <c r="E87" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="K87" t="s">
         <v>595</v>
@@ -7875,7 +7881,7 @@
         <v>162</v>
       </c>
       <c r="O87" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="88" spans="2:15">
@@ -7889,7 +7895,7 @@
         <v>163</v>
       </c>
       <c r="E88" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="K88" t="s">
         <v>595</v>
@@ -7898,7 +7904,7 @@
         <v>584</v>
       </c>
       <c r="M88" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N88" t="s">
         <v>163</v>
@@ -7918,7 +7924,7 @@
         <v>164</v>
       </c>
       <c r="E89" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="K89" t="s">
         <v>596</v>
@@ -7927,13 +7933,13 @@
         <v>590</v>
       </c>
       <c r="M89" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="N89" t="s">
         <v>164</v>
       </c>
       <c r="O89" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="90" spans="2:15">
@@ -7947,7 +7953,7 @@
         <v>165</v>
       </c>
       <c r="E90" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="K90" t="s">
         <v>595</v>
@@ -7976,7 +7982,7 @@
         <v>166</v>
       </c>
       <c r="E91" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K91" t="s">
         <v>596</v>
@@ -8005,7 +8011,7 @@
         <v>167</v>
       </c>
       <c r="E92" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K92" t="s">
         <v>595</v>
@@ -8020,7 +8026,7 @@
         <v>167</v>
       </c>
       <c r="O92" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="93" spans="2:15">
@@ -8034,7 +8040,7 @@
         <v>168</v>
       </c>
       <c r="E93" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="K93" t="s">
         <v>596</v>
@@ -8049,7 +8055,7 @@
         <v>168</v>
       </c>
       <c r="O93" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="94" spans="2:15">
@@ -8063,7 +8069,7 @@
         <v>169</v>
       </c>
       <c r="E94" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="K94" t="s">
         <v>595</v>
@@ -8092,7 +8098,7 @@
         <v>170</v>
       </c>
       <c r="E95" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="K95" t="s">
         <v>595</v>
@@ -8101,7 +8107,7 @@
         <v>584</v>
       </c>
       <c r="M95" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="N95" t="s">
         <v>170</v>
@@ -8121,7 +8127,7 @@
         <v>171</v>
       </c>
       <c r="E96" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="K96" t="s">
         <v>595</v>
@@ -8130,13 +8136,13 @@
         <v>584</v>
       </c>
       <c r="M96" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="N96" t="s">
         <v>171</v>
       </c>
       <c r="O96" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="97" spans="2:15">
@@ -8150,22 +8156,22 @@
         <v>172</v>
       </c>
       <c r="E97" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="K97" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="L97" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="M97" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="N97" t="s">
         <v>172</v>
       </c>
       <c r="O97" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="98" spans="2:15">
@@ -8179,7 +8185,7 @@
         <v>173</v>
       </c>
       <c r="E98" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="K98" t="s">
         <v>596</v>
@@ -8188,13 +8194,13 @@
         <v>588</v>
       </c>
       <c r="M98" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="N98" t="s">
         <v>173</v>
       </c>
       <c r="O98" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="99" spans="2:15">
@@ -8208,7 +8214,7 @@
         <v>174</v>
       </c>
       <c r="E99" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K99" t="s">
         <v>595</v>
@@ -8217,7 +8223,7 @@
         <v>585</v>
       </c>
       <c r="M99" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="N99" t="s">
         <v>174</v>
@@ -8237,7 +8243,7 @@
         <v>175</v>
       </c>
       <c r="E100" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="K100" t="s">
         <v>596</v>
@@ -8246,13 +8252,13 @@
         <v>588</v>
       </c>
       <c r="M100" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="N100" t="s">
         <v>175</v>
       </c>
       <c r="O100" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="101" spans="2:15">
@@ -8266,7 +8272,7 @@
         <v>176</v>
       </c>
       <c r="E101" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K101" t="s">
         <v>596</v>
@@ -8275,13 +8281,13 @@
         <v>588</v>
       </c>
       <c r="M101" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="N101" t="s">
         <v>176</v>
       </c>
       <c r="O101" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="102" spans="2:15">
@@ -8295,13 +8301,13 @@
         <v>177</v>
       </c>
       <c r="E102" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="K102" t="s">
         <v>595</v>
       </c>
       <c r="L102" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="M102" t="s">
         <v>440</v>
@@ -8310,7 +8316,7 @@
         <v>177</v>
       </c>
       <c r="O102" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="103" spans="2:15">
@@ -8324,7 +8330,7 @@
         <v>178</v>
       </c>
       <c r="E103" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="K103" t="s">
         <v>595</v>
@@ -8333,7 +8339,7 @@
         <v>584</v>
       </c>
       <c r="M103" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N103" t="s">
         <v>178</v>
@@ -8353,7 +8359,7 @@
         <v>179</v>
       </c>
       <c r="E104" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="K104" t="s">
         <v>595</v>
@@ -8362,13 +8368,13 @@
         <v>585</v>
       </c>
       <c r="M104" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="N104" t="s">
         <v>179</v>
       </c>
       <c r="O104" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="105" spans="2:15">
@@ -8382,7 +8388,7 @@
         <v>180</v>
       </c>
       <c r="E105" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K105" t="s">
         <v>595</v>
@@ -8391,13 +8397,13 @@
         <v>584</v>
       </c>
       <c r="M105" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="N105" t="s">
         <v>180</v>
       </c>
       <c r="O105" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="106" spans="2:15">
@@ -8411,7 +8417,7 @@
         <v>181</v>
       </c>
       <c r="E106" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="K106" t="s">
         <v>595</v>
@@ -8420,13 +8426,13 @@
         <v>585</v>
       </c>
       <c r="M106" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="N106" t="s">
         <v>181</v>
       </c>
       <c r="O106" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="107" spans="2:15">
@@ -8440,7 +8446,7 @@
         <v>182</v>
       </c>
       <c r="E107" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="K107" t="s">
         <v>595</v>
@@ -8449,7 +8455,7 @@
         <v>585</v>
       </c>
       <c r="M107" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N107" t="s">
         <v>182</v>
@@ -8469,16 +8475,16 @@
         <v>183</v>
       </c>
       <c r="E108" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="K108" t="s">
         <v>595</v>
       </c>
       <c r="L108" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="M108" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="N108" t="s">
         <v>183</v>
@@ -8498,7 +8504,7 @@
         <v>184</v>
       </c>
       <c r="E109" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="K109" t="s">
         <v>595</v>
@@ -8507,13 +8513,13 @@
         <v>585</v>
       </c>
       <c r="M109" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="N109" t="s">
         <v>184</v>
       </c>
       <c r="O109" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="110" spans="2:15">
@@ -8527,16 +8533,16 @@
         <v>185</v>
       </c>
       <c r="E110" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="K110" t="s">
         <v>595</v>
       </c>
       <c r="L110" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="M110" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="N110" t="s">
         <v>185</v>
@@ -8556,7 +8562,7 @@
         <v>186</v>
       </c>
       <c r="E111" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="K111" t="s">
         <v>595</v>
@@ -8565,7 +8571,7 @@
         <v>585</v>
       </c>
       <c r="M111" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="N111" t="s">
         <v>186</v>
@@ -8585,7 +8591,7 @@
         <v>187</v>
       </c>
       <c r="E112" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="K112" t="s">
         <v>595</v>
@@ -8594,13 +8600,13 @@
         <v>584</v>
       </c>
       <c r="M112" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="N112" t="s">
         <v>187</v>
       </c>
       <c r="O112" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="113" spans="2:15">
@@ -8614,7 +8620,7 @@
         <v>188</v>
       </c>
       <c r="E113" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="K113" t="s">
         <v>595</v>
@@ -8629,7 +8635,7 @@
         <v>188</v>
       </c>
       <c r="O113" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="114" spans="2:15">
@@ -8643,7 +8649,7 @@
         <v>189</v>
       </c>
       <c r="E114" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="K114" t="s">
         <v>595</v>
@@ -8652,7 +8658,7 @@
         <v>589</v>
       </c>
       <c r="M114" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="N114" t="s">
         <v>189</v>
@@ -8672,7 +8678,7 @@
         <v>190</v>
       </c>
       <c r="E115" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="K115" t="s">
         <v>595</v>
@@ -8681,7 +8687,7 @@
         <v>589</v>
       </c>
       <c r="M115" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="N115" t="s">
         <v>190</v>
@@ -8701,7 +8707,7 @@
         <v>191</v>
       </c>
       <c r="E116" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="K116" t="s">
         <v>595</v>
@@ -8710,7 +8716,7 @@
         <v>589</v>
       </c>
       <c r="M116" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="N116" t="s">
         <v>191</v>
@@ -8730,7 +8736,7 @@
         <v>192</v>
       </c>
       <c r="E117" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="K117" t="s">
         <v>595</v>
@@ -8759,7 +8765,7 @@
         <v>193</v>
       </c>
       <c r="E118" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="K118" t="s">
         <v>595</v>
@@ -8788,7 +8794,7 @@
         <v>194</v>
       </c>
       <c r="E119" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="K119" t="s">
         <v>595</v>
@@ -8797,7 +8803,7 @@
         <v>585</v>
       </c>
       <c r="M119" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N119" t="s">
         <v>194</v>
@@ -8817,7 +8823,7 @@
         <v>195</v>
       </c>
       <c r="E120" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="K120" t="s">
         <v>596</v>
@@ -8846,7 +8852,7 @@
         <v>196</v>
       </c>
       <c r="E121" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="K121" t="s">
         <v>596</v>
@@ -8861,7 +8867,7 @@
         <v>196</v>
       </c>
       <c r="O121" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="122" spans="2:15">
@@ -8875,7 +8881,7 @@
         <v>197</v>
       </c>
       <c r="E122" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K122" t="s">
         <v>596</v>
@@ -8884,13 +8890,13 @@
         <v>588</v>
       </c>
       <c r="M122" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N122" t="s">
         <v>197</v>
       </c>
       <c r="O122" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="123" spans="2:15">
@@ -8904,7 +8910,7 @@
         <v>198</v>
       </c>
       <c r="E123" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="K123" t="s">
         <v>596</v>
@@ -8913,7 +8919,7 @@
         <v>588</v>
       </c>
       <c r="M123" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N123" t="s">
         <v>198</v>
@@ -8933,7 +8939,7 @@
         <v>199</v>
       </c>
       <c r="E124" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="K124" t="s">
         <v>596</v>
@@ -8942,13 +8948,13 @@
         <v>20</v>
       </c>
       <c r="M124" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="N124" t="s">
         <v>199</v>
       </c>
       <c r="O124" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="125" spans="2:15">
@@ -8962,7 +8968,7 @@
         <v>200</v>
       </c>
       <c r="E125" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="K125" t="s">
         <v>596</v>
@@ -8977,7 +8983,7 @@
         <v>200</v>
       </c>
       <c r="O125" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="126" spans="2:15">
@@ -8991,7 +8997,7 @@
         <v>201</v>
       </c>
       <c r="E126" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="K126" t="s">
         <v>596</v>
@@ -9000,13 +9006,13 @@
         <v>20</v>
       </c>
       <c r="M126" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="N126" t="s">
         <v>201</v>
       </c>
       <c r="O126" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="127" spans="2:15">
@@ -9020,7 +9026,7 @@
         <v>202</v>
       </c>
       <c r="E127" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="K127" t="s">
         <v>596</v>
@@ -9029,13 +9035,13 @@
         <v>588</v>
       </c>
       <c r="M127" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="N127" t="s">
         <v>202</v>
       </c>
       <c r="O127" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="128" spans="2:15">
@@ -9049,7 +9055,7 @@
         <v>203</v>
       </c>
       <c r="E128" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="K128" t="s">
         <v>595</v>
@@ -9058,13 +9064,13 @@
         <v>585</v>
       </c>
       <c r="M128" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="N128" t="s">
         <v>203</v>
       </c>
       <c r="O128" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="129" spans="2:15">
@@ -9078,7 +9084,7 @@
         <v>204</v>
       </c>
       <c r="E129" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="K129" t="s">
         <v>595</v>
@@ -9107,7 +9113,7 @@
         <v>205</v>
       </c>
       <c r="E130" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K130" t="s">
         <v>596</v>
@@ -9116,7 +9122,7 @@
         <v>588</v>
       </c>
       <c r="M130" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N130" t="s">
         <v>205</v>
@@ -9136,7 +9142,7 @@
         <v>206</v>
       </c>
       <c r="E131" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="K131" t="s">
         <v>595</v>
@@ -9145,7 +9151,7 @@
         <v>584</v>
       </c>
       <c r="M131" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="N131" t="s">
         <v>206</v>
@@ -9165,7 +9171,7 @@
         <v>207</v>
       </c>
       <c r="E132" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="K132" t="s">
         <v>595</v>
@@ -9174,13 +9180,13 @@
         <v>585</v>
       </c>
       <c r="M132" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N132" t="s">
         <v>207</v>
       </c>
       <c r="O132" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="133" spans="2:15">
@@ -9194,7 +9200,7 @@
         <v>208</v>
       </c>
       <c r="E133" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K133" t="s">
         <v>595</v>
@@ -9223,7 +9229,7 @@
         <v>209</v>
       </c>
       <c r="E134" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="K134" t="s">
         <v>595</v>
@@ -9232,7 +9238,7 @@
         <v>585</v>
       </c>
       <c r="M134" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="N134" t="s">
         <v>209</v>
@@ -9252,7 +9258,7 @@
         <v>210</v>
       </c>
       <c r="E135" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="K135" t="s">
         <v>596</v>
@@ -9261,13 +9267,13 @@
         <v>588</v>
       </c>
       <c r="M135" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="N135" t="s">
         <v>210</v>
       </c>
       <c r="O135" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="136" spans="2:15">
@@ -9281,7 +9287,7 @@
         <v>211</v>
       </c>
       <c r="E136" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="K136" t="s">
         <v>596</v>
@@ -9290,13 +9296,13 @@
         <v>588</v>
       </c>
       <c r="M136" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="N136" t="s">
         <v>211</v>
       </c>
       <c r="O136" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="137" spans="2:15">
@@ -9310,7 +9316,7 @@
         <v>212</v>
       </c>
       <c r="E137" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="K137" t="s">
         <v>595</v>
@@ -9319,13 +9325,13 @@
         <v>584</v>
       </c>
       <c r="M137" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="N137" t="s">
         <v>212</v>
       </c>
       <c r="O137" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="138" spans="2:15">
@@ -9339,7 +9345,7 @@
         <v>213</v>
       </c>
       <c r="E138" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="K138" t="s">
         <v>596</v>
@@ -9354,7 +9360,7 @@
         <v>213</v>
       </c>
       <c r="O138" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="139" spans="2:15">
@@ -9368,13 +9374,13 @@
         <v>214</v>
       </c>
       <c r="E139" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="K139" t="s">
         <v>595</v>
       </c>
       <c r="L139" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="M139" t="s">
         <v>440</v>
@@ -9383,7 +9389,7 @@
         <v>214</v>
       </c>
       <c r="O139" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="140" spans="2:15">
@@ -9397,7 +9403,7 @@
         <v>215</v>
       </c>
       <c r="E140" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="K140" t="s">
         <v>595</v>
@@ -9406,13 +9412,13 @@
         <v>589</v>
       </c>
       <c r="M140" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N140" t="s">
         <v>215</v>
       </c>
       <c r="O140" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="141" spans="2:15">
@@ -9426,22 +9432,22 @@
         <v>216</v>
       </c>
       <c r="E141" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K141" t="s">
         <v>595</v>
       </c>
       <c r="L141" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="M141" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="N141" t="s">
         <v>216</v>
       </c>
       <c r="O141" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="142" spans="2:15">
@@ -9455,16 +9461,16 @@
         <v>217</v>
       </c>
       <c r="E142" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="K142" t="s">
         <v>595</v>
       </c>
       <c r="L142" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="M142" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N142" t="s">
         <v>217</v>
@@ -9484,7 +9490,7 @@
         <v>218</v>
       </c>
       <c r="E143" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K143" t="s">
         <v>596</v>
@@ -9493,13 +9499,13 @@
         <v>20</v>
       </c>
       <c r="M143" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="N143" t="s">
         <v>218</v>
       </c>
       <c r="O143" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="144" spans="2:15">
@@ -9513,7 +9519,7 @@
         <v>219</v>
       </c>
       <c r="E144" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="K144" t="s">
         <v>596</v>
@@ -9522,13 +9528,13 @@
         <v>588</v>
       </c>
       <c r="M144" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N144" t="s">
         <v>219</v>
       </c>
       <c r="O144" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="145" spans="2:15">
@@ -9542,7 +9548,7 @@
         <v>220</v>
       </c>
       <c r="E145" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="K145" t="s">
         <v>595</v>
@@ -9557,7 +9563,7 @@
         <v>220</v>
       </c>
       <c r="O145" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="146" spans="2:15">
@@ -9571,7 +9577,7 @@
         <v>221</v>
       </c>
       <c r="E146" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K146" t="s">
         <v>595</v>
@@ -9580,13 +9586,13 @@
         <v>585</v>
       </c>
       <c r="M146" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="N146" t="s">
         <v>221</v>
       </c>
       <c r="O146" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="147" spans="2:15">
@@ -9600,16 +9606,16 @@
         <v>222</v>
       </c>
       <c r="E147" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="K147" t="s">
         <v>596</v>
       </c>
       <c r="L147" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="M147" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="N147" t="s">
         <v>222</v>
@@ -9629,7 +9635,7 @@
         <v>223</v>
       </c>
       <c r="E148" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="K148" t="s">
         <v>595</v>
@@ -9644,7 +9650,7 @@
         <v>223</v>
       </c>
       <c r="O148" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="149" spans="2:15">
@@ -9658,7 +9664,7 @@
         <v>224</v>
       </c>
       <c r="E149" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="K149" t="s">
         <v>596</v>
@@ -9687,7 +9693,7 @@
         <v>225</v>
       </c>
       <c r="E150" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="K150" t="s">
         <v>595</v>
@@ -9702,7 +9708,7 @@
         <v>225</v>
       </c>
       <c r="O150" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="151" spans="2:15">
@@ -9716,7 +9722,7 @@
         <v>226</v>
       </c>
       <c r="E151" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="K151" t="s">
         <v>596</v>
@@ -9725,7 +9731,7 @@
         <v>20</v>
       </c>
       <c r="M151" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="N151" t="s">
         <v>226</v>
@@ -9745,7 +9751,7 @@
         <v>227</v>
       </c>
       <c r="E152" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="K152" t="s">
         <v>595</v>
@@ -9760,7 +9766,7 @@
         <v>227</v>
       </c>
       <c r="O152" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="153" spans="2:15">
@@ -9774,7 +9780,7 @@
         <v>228</v>
       </c>
       <c r="E153" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="K153" t="s">
         <v>595</v>
@@ -9789,7 +9795,7 @@
         <v>228</v>
       </c>
       <c r="O153" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="154" spans="2:15">
@@ -9803,7 +9809,7 @@
         <v>229</v>
       </c>
       <c r="E154" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="K154" t="s">
         <v>595</v>
@@ -9832,7 +9838,7 @@
         <v>230</v>
       </c>
       <c r="E155" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K155" t="s">
         <v>595</v>
@@ -9847,7 +9853,7 @@
         <v>230</v>
       </c>
       <c r="O155" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="156" spans="2:15">
@@ -9861,7 +9867,7 @@
         <v>231</v>
       </c>
       <c r="E156" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="K156" t="s">
         <v>596</v>
@@ -9876,7 +9882,7 @@
         <v>231</v>
       </c>
       <c r="O156" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="157" spans="2:15">
@@ -9890,7 +9896,7 @@
         <v>232</v>
       </c>
       <c r="E157" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K157" t="s">
         <v>595</v>
@@ -9905,7 +9911,7 @@
         <v>232</v>
       </c>
       <c r="O157" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="158" spans="2:15">
@@ -9919,7 +9925,7 @@
         <v>233</v>
       </c>
       <c r="E158" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="K158" t="s">
         <v>596</v>
@@ -9928,13 +9934,13 @@
         <v>588</v>
       </c>
       <c r="M158" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="N158" t="s">
         <v>233</v>
       </c>
       <c r="O158" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="159" spans="2:15">
@@ -9948,7 +9954,7 @@
         <v>234</v>
       </c>
       <c r="E159" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="K159" t="s">
         <v>595</v>
@@ -9957,13 +9963,13 @@
         <v>585</v>
       </c>
       <c r="M159" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N159" t="s">
         <v>234</v>
       </c>
       <c r="O159" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="160" spans="2:15">
@@ -9977,7 +9983,7 @@
         <v>235</v>
       </c>
       <c r="E160" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="K160" t="s">
         <v>595</v>
@@ -9986,7 +9992,7 @@
         <v>585</v>
       </c>
       <c r="M160" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N160" t="s">
         <v>235</v>
@@ -10006,7 +10012,7 @@
         <v>236</v>
       </c>
       <c r="E161" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="K161" t="s">
         <v>596</v>
@@ -10015,13 +10021,13 @@
         <v>588</v>
       </c>
       <c r="M161" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="N161" t="s">
         <v>236</v>
       </c>
       <c r="O161" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="162" spans="2:15">
@@ -10035,7 +10041,7 @@
         <v>237</v>
       </c>
       <c r="E162" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="K162" t="s">
         <v>595</v>
@@ -10050,7 +10056,7 @@
         <v>237</v>
       </c>
       <c r="O162" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="163" spans="2:15">
@@ -10064,7 +10070,7 @@
         <v>238</v>
       </c>
       <c r="E163" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="K163" t="s">
         <v>595</v>
@@ -10093,7 +10099,7 @@
         <v>239</v>
       </c>
       <c r="E164" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K164" t="s">
         <v>595</v>
@@ -10102,7 +10108,7 @@
         <v>584</v>
       </c>
       <c r="M164" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="N164" t="s">
         <v>239</v>
@@ -10122,28 +10128,28 @@
         <v>240</v>
       </c>
       <c r="E165" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="I165" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="K165" t="s">
         <v>595</v>
       </c>
       <c r="L165" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="M165" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N165" t="s">
         <v>240</v>
       </c>
       <c r="O165" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="166" spans="2:15">
@@ -10157,7 +10163,7 @@
         <v>241</v>
       </c>
       <c r="E166" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="K166" t="s">
         <v>596</v>
@@ -10172,7 +10178,7 @@
         <v>241</v>
       </c>
       <c r="O166" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="167" spans="2:15">
@@ -10186,7 +10192,7 @@
         <v>242</v>
       </c>
       <c r="E167" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="K167" t="s">
         <v>596</v>
@@ -10195,13 +10201,13 @@
         <v>20</v>
       </c>
       <c r="M167" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="N167" t="s">
         <v>242</v>
       </c>
       <c r="O167" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="168" spans="2:15">
@@ -10215,7 +10221,7 @@
         <v>243</v>
       </c>
       <c r="E168" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="K168" t="s">
         <v>596</v>
@@ -10224,13 +10230,13 @@
         <v>20</v>
       </c>
       <c r="M168" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="N168" t="s">
         <v>243</v>
       </c>
       <c r="O168" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="169" spans="2:15">
@@ -10244,7 +10250,7 @@
         <v>244</v>
       </c>
       <c r="E169" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="K169" t="s">
         <v>595</v>
@@ -10259,7 +10265,7 @@
         <v>244</v>
       </c>
       <c r="O169" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="170" spans="2:15">
@@ -10273,7 +10279,7 @@
         <v>245</v>
       </c>
       <c r="E170" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="K170" t="s">
         <v>596</v>
@@ -10302,7 +10308,7 @@
         <v>246</v>
       </c>
       <c r="E171" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="K171" t="s">
         <v>595</v>
@@ -10311,13 +10317,13 @@
         <v>584</v>
       </c>
       <c r="M171" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="N171" t="s">
         <v>246</v>
       </c>
       <c r="O171" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="172" spans="2:15">
@@ -10331,7 +10337,7 @@
         <v>247</v>
       </c>
       <c r="E172" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="K172" t="s">
         <v>596</v>
@@ -10346,7 +10352,7 @@
         <v>247</v>
       </c>
       <c r="O172" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="173" spans="2:15">
@@ -10360,7 +10366,7 @@
         <v>248</v>
       </c>
       <c r="E173" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K173" t="s">
         <v>603</v>
@@ -10369,7 +10375,7 @@
         <v>592</v>
       </c>
       <c r="M173" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N173" t="s">
         <v>248</v>
@@ -10389,7 +10395,7 @@
         <v>249</v>
       </c>
       <c r="E174" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K174" t="s">
         <v>596</v>
@@ -10398,13 +10404,13 @@
         <v>20</v>
       </c>
       <c r="M174" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="N174" t="s">
         <v>249</v>
       </c>
       <c r="O174" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="175" spans="2:15">
@@ -10418,7 +10424,7 @@
         <v>250</v>
       </c>
       <c r="E175" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="K175" t="s">
         <v>594</v>
@@ -10433,7 +10439,7 @@
         <v>250</v>
       </c>
       <c r="O175" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="176" spans="2:15">
@@ -10447,7 +10453,7 @@
         <v>251</v>
       </c>
       <c r="E176" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="K176" t="s">
         <v>596</v>
@@ -10456,7 +10462,7 @@
         <v>20</v>
       </c>
       <c r="M176" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="N176" t="s">
         <v>251</v>
@@ -10476,7 +10482,7 @@
         <v>252</v>
       </c>
       <c r="E177" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="K177" t="s">
         <v>599</v>
@@ -10485,7 +10491,7 @@
         <v>584</v>
       </c>
       <c r="M177" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="N177" t="s">
         <v>252</v>
@@ -10505,7 +10511,7 @@
         <v>253</v>
       </c>
       <c r="E178" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="K178" t="s">
         <v>595</v>
@@ -10514,13 +10520,13 @@
         <v>584</v>
       </c>
       <c r="M178" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="N178" t="s">
         <v>253</v>
       </c>
       <c r="O178" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="179" spans="2:15">
@@ -10534,7 +10540,7 @@
         <v>254</v>
       </c>
       <c r="E179" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="K179" t="s">
         <v>595</v>
@@ -10543,7 +10549,7 @@
         <v>584</v>
       </c>
       <c r="M179" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="N179" t="s">
         <v>254</v>
@@ -10563,7 +10569,7 @@
         <v>255</v>
       </c>
       <c r="E180" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="K180" t="s">
         <v>599</v>
@@ -10592,7 +10598,7 @@
         <v>256</v>
       </c>
       <c r="E181" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="K181" t="s">
         <v>595</v>
@@ -10601,13 +10607,13 @@
         <v>585</v>
       </c>
       <c r="M181" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="N181" t="s">
         <v>256</v>
       </c>
       <c r="O181" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="182" spans="2:15">
@@ -10621,13 +10627,13 @@
         <v>257</v>
       </c>
       <c r="E182" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="K182" t="s">
         <v>596</v>
       </c>
       <c r="L182" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="M182" t="s">
         <v>461</v>
@@ -10650,7 +10656,7 @@
         <v>258</v>
       </c>
       <c r="E183" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K183" t="s">
         <v>595</v>
@@ -10665,7 +10671,7 @@
         <v>258</v>
       </c>
       <c r="O183" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="184" spans="2:15">
@@ -10679,7 +10685,7 @@
         <v>259</v>
       </c>
       <c r="E184" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="K184" t="s">
         <v>595</v>
@@ -10688,13 +10694,13 @@
         <v>584</v>
       </c>
       <c r="M184" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N184" t="s">
         <v>259</v>
       </c>
       <c r="O184" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="185" spans="2:15">
@@ -10708,7 +10714,7 @@
         <v>260</v>
       </c>
       <c r="E185" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="K185" t="s">
         <v>603</v>
@@ -10717,13 +10723,13 @@
         <v>592</v>
       </c>
       <c r="M185" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="N185" t="s">
         <v>260</v>
       </c>
       <c r="O185" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="186" spans="2:15">
@@ -10737,10 +10743,10 @@
         <v>261</v>
       </c>
       <c r="E186" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F186" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="K186" t="s">
         <v>596</v>
@@ -10749,13 +10755,13 @@
         <v>20</v>
       </c>
       <c r="M186" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="N186" t="s">
         <v>261</v>
       </c>
       <c r="O186" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="187" spans="2:15">
@@ -10769,7 +10775,7 @@
         <v>262</v>
       </c>
       <c r="E187" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="K187" t="s">
         <v>595</v>
@@ -10778,13 +10784,13 @@
         <v>585</v>
       </c>
       <c r="M187" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="N187" t="s">
         <v>262</v>
       </c>
       <c r="O187" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="188" spans="2:15">
@@ -10798,7 +10804,7 @@
         <v>263</v>
       </c>
       <c r="E188" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="K188" t="s">
         <v>595</v>
@@ -10813,7 +10819,7 @@
         <v>263</v>
       </c>
       <c r="O188" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="189" spans="2:15">
@@ -10827,7 +10833,7 @@
         <v>264</v>
       </c>
       <c r="E189" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="K189" t="s">
         <v>595</v>
@@ -10836,13 +10842,13 @@
         <v>584</v>
       </c>
       <c r="M189" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N189" t="s">
         <v>264</v>
       </c>
       <c r="O189" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="190" spans="2:15">
@@ -10856,7 +10862,7 @@
         <v>265</v>
       </c>
       <c r="E190" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="K190" t="s">
         <v>595</v>
@@ -10865,13 +10871,13 @@
         <v>592</v>
       </c>
       <c r="M190" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="N190" t="s">
         <v>265</v>
       </c>
       <c r="O190" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="191" spans="2:15">
@@ -10885,7 +10891,7 @@
         <v>266</v>
       </c>
       <c r="E191" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="K191" t="s">
         <v>595</v>
@@ -10894,13 +10900,13 @@
         <v>592</v>
       </c>
       <c r="M191" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="N191" t="s">
         <v>266</v>
       </c>
       <c r="O191" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="192" spans="2:15">
@@ -10914,7 +10920,7 @@
         <v>267</v>
       </c>
       <c r="E192" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K192" t="s">
         <v>601</v>
@@ -10923,13 +10929,13 @@
         <v>587</v>
       </c>
       <c r="M192" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="N192" t="s">
         <v>267</v>
       </c>
       <c r="O192" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="193" spans="2:15">
@@ -10943,22 +10949,22 @@
         <v>268</v>
       </c>
       <c r="E193" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="K193" t="s">
         <v>601</v>
       </c>
       <c r="L193" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="M193" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="N193" t="s">
         <v>268</v>
       </c>
       <c r="O193" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="194" spans="2:15">
@@ -10972,13 +10978,13 @@
         <v>269</v>
       </c>
       <c r="E194" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F194" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="I194" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="K194" t="s">
         <v>596</v>
@@ -10987,13 +10993,13 @@
         <v>20</v>
       </c>
       <c r="M194" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="N194" t="s">
         <v>269</v>
       </c>
       <c r="O194" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="195" spans="2:15">
@@ -11007,7 +11013,7 @@
         <v>270</v>
       </c>
       <c r="E195" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="K195" t="s">
         <v>599</v>
@@ -11022,7 +11028,7 @@
         <v>270</v>
       </c>
       <c r="O195" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="196" spans="2:15">
@@ -11036,7 +11042,7 @@
         <v>271</v>
       </c>
       <c r="E196" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="K196" t="s">
         <v>599</v>
@@ -11045,13 +11051,13 @@
         <v>20</v>
       </c>
       <c r="M196" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="N196" t="s">
         <v>271</v>
       </c>
       <c r="O196" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="197" spans="2:15">
@@ -11065,7 +11071,7 @@
         <v>272</v>
       </c>
       <c r="E197" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="K197" t="s">
         <v>596</v>
@@ -11074,13 +11080,13 @@
         <v>20</v>
       </c>
       <c r="M197" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="N197" t="s">
         <v>272</v>
       </c>
       <c r="O197" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="198" spans="2:15">
@@ -11094,7 +11100,7 @@
         <v>273</v>
       </c>
       <c r="E198" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="K198" t="s">
         <v>596</v>
@@ -11103,13 +11109,13 @@
         <v>271</v>
       </c>
       <c r="M198" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="N198" t="s">
         <v>273</v>
       </c>
       <c r="O198" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="199" spans="2:15">
@@ -11123,7 +11129,7 @@
         <v>274</v>
       </c>
       <c r="E199" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="K199" t="s">
         <v>595</v>
@@ -11132,13 +11138,13 @@
         <v>584</v>
       </c>
       <c r="M199" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="N199" t="s">
         <v>274</v>
       </c>
       <c r="O199" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="200" spans="2:15">
@@ -11152,22 +11158,22 @@
         <v>275</v>
       </c>
       <c r="E200" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="K200" t="s">
         <v>595</v>
       </c>
       <c r="L200" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="M200" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="N200" t="s">
         <v>275</v>
       </c>
       <c r="O200" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="201" spans="2:15">
@@ -11181,7 +11187,7 @@
         <v>276</v>
       </c>
       <c r="E201" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K201" t="s">
         <v>595</v>
@@ -11190,13 +11196,13 @@
         <v>592</v>
       </c>
       <c r="M201" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="N201" t="s">
         <v>276</v>
       </c>
       <c r="O201" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="202" spans="2:15">
@@ -11210,7 +11216,7 @@
         <v>277</v>
       </c>
       <c r="E202" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K202" t="s">
         <v>601</v>
@@ -11219,7 +11225,7 @@
         <v>584</v>
       </c>
       <c r="M202" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="N202" t="s">
         <v>277</v>
@@ -11239,7 +11245,7 @@
         <v>278</v>
       </c>
       <c r="E203" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K203" t="s">
         <v>595</v>
@@ -11248,13 +11254,13 @@
         <v>592</v>
       </c>
       <c r="M203" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="N203" t="s">
         <v>278</v>
       </c>
       <c r="O203" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="204" spans="2:15">
@@ -11268,7 +11274,7 @@
         <v>279</v>
       </c>
       <c r="E204" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="K204" t="s">
         <v>595</v>
@@ -11277,7 +11283,7 @@
         <v>585</v>
       </c>
       <c r="M204" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N204" t="s">
         <v>279</v>
@@ -11297,7 +11303,7 @@
         <v>280</v>
       </c>
       <c r="E205" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K205" t="s">
         <v>595</v>
@@ -11326,7 +11332,7 @@
         <v>281</v>
       </c>
       <c r="E206" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K206" t="s">
         <v>595</v>
@@ -11335,7 +11341,7 @@
         <v>584</v>
       </c>
       <c r="M206" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="N206" t="s">
         <v>281</v>
@@ -11355,7 +11361,7 @@
         <v>282</v>
       </c>
       <c r="E207" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K207" t="s">
         <v>595</v>
@@ -11370,7 +11376,7 @@
         <v>282</v>
       </c>
       <c r="O207" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="208" spans="2:15">
@@ -11384,7 +11390,7 @@
         <v>283</v>
       </c>
       <c r="E208" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K208" t="s">
         <v>595</v>
@@ -11399,7 +11405,7 @@
         <v>283</v>
       </c>
       <c r="O208" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="209" spans="2:15">
@@ -11413,7 +11419,7 @@
         <v>284</v>
       </c>
       <c r="E209" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="K209" t="s">
         <v>595</v>
@@ -11422,13 +11428,13 @@
         <v>584</v>
       </c>
       <c r="M209" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="N209" t="s">
         <v>284</v>
       </c>
       <c r="O209" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="210" spans="2:15">
@@ -11442,7 +11448,7 @@
         <v>285</v>
       </c>
       <c r="E210" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="K210" t="s">
         <v>595</v>
@@ -11471,7 +11477,7 @@
         <v>286</v>
       </c>
       <c r="E211" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="K211" t="s">
         <v>595</v>
@@ -11500,7 +11506,7 @@
         <v>287</v>
       </c>
       <c r="E212" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K212" t="s">
         <v>596</v>
@@ -11509,13 +11515,13 @@
         <v>592</v>
       </c>
       <c r="M212" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="N212" t="s">
         <v>287</v>
       </c>
       <c r="O212" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="213" spans="2:15">
@@ -11529,7 +11535,7 @@
         <v>288</v>
       </c>
       <c r="E213" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="K213" t="s">
         <v>596</v>
@@ -11538,13 +11544,13 @@
         <v>588</v>
       </c>
       <c r="M213" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="N213" t="s">
         <v>288</v>
       </c>
       <c r="O213" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="214" spans="2:15">
@@ -11558,7 +11564,7 @@
         <v>289</v>
       </c>
       <c r="E214" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="K214" t="s">
         <v>595</v>
@@ -11567,13 +11573,13 @@
         <v>584</v>
       </c>
       <c r="M214" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N214" t="s">
         <v>289</v>
       </c>
       <c r="O214" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="215" spans="2:15">
@@ -11587,7 +11593,7 @@
         <v>290</v>
       </c>
       <c r="E215" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="K215" t="s">
         <v>596</v>
@@ -11616,7 +11622,7 @@
         <v>291</v>
       </c>
       <c r="E216" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="K216" t="s">
         <v>596</v>
@@ -11625,13 +11631,13 @@
         <v>592</v>
       </c>
       <c r="M216" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="N216" t="s">
         <v>291</v>
       </c>
       <c r="O216" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="217" spans="2:15">
@@ -11645,13 +11651,13 @@
         <v>292</v>
       </c>
       <c r="E217" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="K217" t="s">
         <v>596</v>
       </c>
       <c r="L217" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="M217" t="s">
         <v>445</v>
@@ -11674,7 +11680,7 @@
         <v>293</v>
       </c>
       <c r="E218" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="K218" t="s">
         <v>596</v>
@@ -11683,13 +11689,13 @@
         <v>592</v>
       </c>
       <c r="M218" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="N218" t="s">
         <v>293</v>
       </c>
       <c r="O218" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="219" spans="2:15">
@@ -11703,7 +11709,7 @@
         <v>294</v>
       </c>
       <c r="E219" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="K219" t="s">
         <v>603</v>
@@ -11712,13 +11718,13 @@
         <v>592</v>
       </c>
       <c r="M219" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N219" t="s">
         <v>294</v>
       </c>
       <c r="O219" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="220" spans="2:15">
@@ -11732,7 +11738,7 @@
         <v>295</v>
       </c>
       <c r="E220" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K220" t="s">
         <v>601</v>
@@ -11741,7 +11747,7 @@
         <v>587</v>
       </c>
       <c r="M220" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N220" t="s">
         <v>295</v>
@@ -11761,7 +11767,7 @@
         <v>296</v>
       </c>
       <c r="E221" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="K221" t="s">
         <v>598</v>
@@ -11770,7 +11776,7 @@
         <v>594</v>
       </c>
       <c r="M221" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="N221" t="s">
         <v>296</v>
@@ -11790,7 +11796,7 @@
         <v>297</v>
       </c>
       <c r="E222" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="K222" t="s">
         <v>598</v>
@@ -11799,7 +11805,7 @@
         <v>665</v>
       </c>
       <c r="M222" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="N222" t="s">
         <v>297</v>
@@ -11819,7 +11825,7 @@
         <v>298</v>
       </c>
       <c r="E223" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="K223" t="s">
         <v>598</v>
@@ -11834,7 +11840,7 @@
         <v>298</v>
       </c>
       <c r="O223" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="224" spans="2:15">
@@ -11848,7 +11854,7 @@
         <v>299</v>
       </c>
       <c r="E224" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="K224" t="s">
         <v>598</v>
@@ -11857,13 +11863,13 @@
         <v>594</v>
       </c>
       <c r="M224" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="N224" t="s">
         <v>299</v>
       </c>
       <c r="O224" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="225" spans="2:15">
@@ -11877,7 +11883,7 @@
         <v>300</v>
       </c>
       <c r="E225" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="K225" t="s">
         <v>598</v>
@@ -11886,13 +11892,13 @@
         <v>594</v>
       </c>
       <c r="M225" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="N225" t="s">
         <v>300</v>
       </c>
       <c r="O225" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="226" spans="2:15">
@@ -11906,7 +11912,7 @@
         <v>301</v>
       </c>
       <c r="E226" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="K226" t="s">
         <v>596</v>
@@ -11915,7 +11921,7 @@
         <v>589</v>
       </c>
       <c r="M226" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="N226" t="s">
         <v>301</v>
@@ -11935,7 +11941,7 @@
         <v>302</v>
       </c>
       <c r="E227" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="K227" t="s">
         <v>595</v>
@@ -11944,13 +11950,13 @@
         <v>589</v>
       </c>
       <c r="M227" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="N227" t="s">
         <v>302</v>
       </c>
       <c r="O227" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="228" spans="2:15">
@@ -11964,7 +11970,7 @@
         <v>303</v>
       </c>
       <c r="E228" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="K228" t="s">
         <v>595</v>
@@ -11993,7 +11999,7 @@
         <v>304</v>
       </c>
       <c r="E229" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="K229" t="s">
         <v>596</v>
@@ -12008,7 +12014,7 @@
         <v>304</v>
       </c>
       <c r="O229" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="230" spans="2:15">
@@ -12022,7 +12028,7 @@
         <v>305</v>
       </c>
       <c r="E230" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="K230" t="s">
         <v>595</v>
@@ -12031,13 +12037,13 @@
         <v>592</v>
       </c>
       <c r="M230" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="N230" t="s">
         <v>305</v>
       </c>
       <c r="O230" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="231" spans="2:15">
@@ -12051,16 +12057,16 @@
         <v>306</v>
       </c>
       <c r="E231" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K231" t="s">
         <v>596</v>
       </c>
       <c r="L231" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="M231" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="N231" t="s">
         <v>306</v>
@@ -12080,7 +12086,7 @@
         <v>307</v>
       </c>
       <c r="E232" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="K232" t="s">
         <v>596</v>
@@ -12089,13 +12095,13 @@
         <v>592</v>
       </c>
       <c r="M232" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N232" t="s">
         <v>307</v>
       </c>
       <c r="O232" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="233" spans="2:15">
@@ -12109,7 +12115,7 @@
         <v>308</v>
       </c>
       <c r="E233" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="K233" t="s">
         <v>601</v>
@@ -12124,7 +12130,7 @@
         <v>308</v>
       </c>
       <c r="O233" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="234" spans="2:15">
@@ -12138,7 +12144,7 @@
         <v>309</v>
       </c>
       <c r="E234" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="K234" t="s">
         <v>598</v>
@@ -12147,7 +12153,7 @@
         <v>594</v>
       </c>
       <c r="M234" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="N234" t="s">
         <v>309</v>
@@ -12167,7 +12173,7 @@
         <v>310</v>
       </c>
       <c r="E235" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="K235" t="s">
         <v>598</v>
@@ -12176,13 +12182,13 @@
         <v>594</v>
       </c>
       <c r="M235" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="N235" t="s">
         <v>310</v>
       </c>
       <c r="O235" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="236" spans="2:15">
@@ -12196,7 +12202,7 @@
         <v>311</v>
       </c>
       <c r="E236" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="K236" t="s">
         <v>595</v>
@@ -12205,13 +12211,13 @@
         <v>584</v>
       </c>
       <c r="M236" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="N236" t="s">
         <v>311</v>
       </c>
       <c r="O236" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="237" spans="2:15">
@@ -12225,7 +12231,7 @@
         <v>312</v>
       </c>
       <c r="E237" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="K237" t="s">
         <v>595</v>
@@ -12240,7 +12246,7 @@
         <v>312</v>
       </c>
       <c r="O237" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="238" spans="2:15">
@@ -12254,7 +12260,7 @@
         <v>313</v>
       </c>
       <c r="E238" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="K238" t="s">
         <v>602</v>
@@ -12263,13 +12269,13 @@
         <v>592</v>
       </c>
       <c r="M238" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="N238" t="s">
         <v>313</v>
       </c>
       <c r="O238" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="239" spans="2:15">
@@ -12283,7 +12289,7 @@
         <v>314</v>
       </c>
       <c r="E239" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="K239" t="s">
         <v>596</v>
@@ -12292,7 +12298,7 @@
         <v>583</v>
       </c>
       <c r="M239" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N239" t="s">
         <v>314</v>
@@ -12312,7 +12318,7 @@
         <v>315</v>
       </c>
       <c r="E240" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="K240" t="s">
         <v>596</v>
@@ -12321,13 +12327,13 @@
         <v>583</v>
       </c>
       <c r="M240" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N240" t="s">
         <v>315</v>
       </c>
       <c r="O240" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="241" spans="2:15">
@@ -12341,7 +12347,7 @@
         <v>316</v>
       </c>
       <c r="E241" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="K241" t="s">
         <v>596</v>
@@ -12356,7 +12362,7 @@
         <v>316</v>
       </c>
       <c r="O241" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="242" spans="2:15">
@@ -12370,7 +12376,7 @@
         <v>317</v>
       </c>
       <c r="E242" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="K242" t="s">
         <v>596</v>
@@ -12379,13 +12385,13 @@
         <v>583</v>
       </c>
       <c r="M242" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="N242" t="s">
         <v>317</v>
       </c>
       <c r="O242" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="243" spans="2:15">
@@ -12399,7 +12405,7 @@
         <v>318</v>
       </c>
       <c r="E243" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="K243" t="s">
         <v>596</v>
@@ -12428,7 +12434,7 @@
         <v>319</v>
       </c>
       <c r="E244" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="K244" t="s">
         <v>596</v>
@@ -12443,7 +12449,7 @@
         <v>319</v>
       </c>
       <c r="O244" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="245" spans="2:15">
@@ -12457,7 +12463,7 @@
         <v>320</v>
       </c>
       <c r="E245" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="K245" t="s">
         <v>596</v>
@@ -12472,7 +12478,7 @@
         <v>320</v>
       </c>
       <c r="O245" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="246" spans="2:15">
@@ -12486,13 +12492,13 @@
         <v>321</v>
       </c>
       <c r="E246" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="I246" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="K246" t="s">
         <v>595</v>
@@ -12501,13 +12507,13 @@
         <v>584</v>
       </c>
       <c r="M246" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N246" t="s">
         <v>321</v>
       </c>
       <c r="O246" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="247" spans="2:15">
@@ -12521,7 +12527,7 @@
         <v>322</v>
       </c>
       <c r="E247" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K247" t="s">
         <v>595</v>
@@ -12530,7 +12536,7 @@
         <v>584</v>
       </c>
       <c r="M247" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N247" t="s">
         <v>322</v>
@@ -12550,7 +12556,7 @@
         <v>323</v>
       </c>
       <c r="E248" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="K248" t="s">
         <v>595</v>
@@ -12579,7 +12585,7 @@
         <v>324</v>
       </c>
       <c r="E249" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="K249" t="s">
         <v>592</v>
@@ -12588,13 +12594,13 @@
         <v>588</v>
       </c>
       <c r="M249" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="N249" t="s">
         <v>324</v>
       </c>
       <c r="O249" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="250" spans="2:15">
@@ -12608,7 +12614,7 @@
         <v>325</v>
       </c>
       <c r="E250" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="K250" t="s">
         <v>596</v>
@@ -12617,13 +12623,13 @@
         <v>592</v>
       </c>
       <c r="M250" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="N250" t="s">
         <v>325</v>
       </c>
       <c r="O250" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="251" spans="2:15">
@@ -12637,10 +12643,10 @@
         <v>326</v>
       </c>
       <c r="E251" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F251" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="K251" t="s">
         <v>596</v>
@@ -12649,13 +12655,13 @@
         <v>592</v>
       </c>
       <c r="M251" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="N251" t="s">
         <v>326</v>
       </c>
       <c r="O251" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="252" spans="2:15">
@@ -12669,7 +12675,7 @@
         <v>327</v>
       </c>
       <c r="E252" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K252" t="s">
         <v>595</v>
@@ -12678,13 +12684,13 @@
         <v>588</v>
       </c>
       <c r="M252" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N252" t="s">
         <v>327</v>
       </c>
       <c r="O252" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="253" spans="2:15">
@@ -12698,7 +12704,7 @@
         <v>328</v>
       </c>
       <c r="E253" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="K253" t="s">
         <v>603</v>
@@ -12707,13 +12713,13 @@
         <v>592</v>
       </c>
       <c r="M253" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N253" t="s">
         <v>328</v>
       </c>
       <c r="O253" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="254" spans="2:15">
@@ -12727,7 +12733,7 @@
         <v>329</v>
       </c>
       <c r="E254" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K254" t="s">
         <v>596</v>
@@ -12736,7 +12742,7 @@
         <v>592</v>
       </c>
       <c r="M254" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="N254" t="s">
         <v>329</v>
@@ -12756,7 +12762,7 @@
         <v>330</v>
       </c>
       <c r="E255" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K255" t="s">
         <v>603</v>
@@ -12765,7 +12771,7 @@
         <v>592</v>
       </c>
       <c r="M255" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="N255" t="s">
         <v>330</v>
@@ -12785,7 +12791,7 @@
         <v>331</v>
       </c>
       <c r="E256" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K256" t="s">
         <v>603</v>
@@ -12794,13 +12800,13 @@
         <v>592</v>
       </c>
       <c r="M256" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="N256" t="s">
         <v>331</v>
       </c>
       <c r="O256" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="257" spans="2:15">
@@ -12814,7 +12820,7 @@
         <v>332</v>
       </c>
       <c r="E257" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="K257" t="s">
         <v>603</v>
@@ -12823,13 +12829,13 @@
         <v>592</v>
       </c>
       <c r="M257" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N257" t="s">
         <v>332</v>
       </c>
       <c r="O257" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="258" spans="2:15">
@@ -12843,7 +12849,7 @@
         <v>333</v>
       </c>
       <c r="E258" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="K258" t="s">
         <v>603</v>
@@ -12858,7 +12864,7 @@
         <v>333</v>
       </c>
       <c r="O258" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="259" spans="2:15">
@@ -12872,7 +12878,7 @@
         <v>334</v>
       </c>
       <c r="E259" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="K259" t="s">
         <v>596</v>
@@ -12881,7 +12887,7 @@
         <v>592</v>
       </c>
       <c r="M259" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="N259" t="s">
         <v>334</v>
@@ -12901,7 +12907,7 @@
         <v>335</v>
       </c>
       <c r="E260" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K260" t="s">
         <v>596</v>
@@ -12910,13 +12916,13 @@
         <v>590</v>
       </c>
       <c r="M260" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="N260" t="s">
         <v>335</v>
       </c>
       <c r="O260" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="261" spans="2:15">
@@ -12930,7 +12936,7 @@
         <v>336</v>
       </c>
       <c r="E261" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="K261" t="s">
         <v>603</v>
@@ -12939,13 +12945,13 @@
         <v>590</v>
       </c>
       <c r="M261" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="N261" t="s">
         <v>336</v>
       </c>
       <c r="O261" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="262" spans="2:15">
@@ -12959,7 +12965,7 @@
         <v>337</v>
       </c>
       <c r="E262" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="K262" t="s">
         <v>602</v>
@@ -12968,13 +12974,13 @@
         <v>590</v>
       </c>
       <c r="M262" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N262" t="s">
         <v>337</v>
       </c>
       <c r="O262" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="263" spans="2:15">
@@ -12988,7 +12994,7 @@
         <v>338</v>
       </c>
       <c r="E263" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="K263" t="s">
         <v>595</v>
@@ -12997,13 +13003,13 @@
         <v>591</v>
       </c>
       <c r="M263" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="N263" t="s">
         <v>338</v>
       </c>
       <c r="O263" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="264" spans="2:15">
@@ -13017,7 +13023,7 @@
         <v>339</v>
       </c>
       <c r="E264" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="K264" t="s">
         <v>595</v>
@@ -13026,13 +13032,13 @@
         <v>591</v>
       </c>
       <c r="M264" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="N264" t="s">
         <v>339</v>
       </c>
       <c r="O264" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="265" spans="2:15">
@@ -13046,7 +13052,7 @@
         <v>340</v>
       </c>
       <c r="E265" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="K265" t="s">
         <v>600</v>
@@ -13055,13 +13061,13 @@
         <v>594</v>
       </c>
       <c r="M265" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="N265" t="s">
         <v>340</v>
       </c>
       <c r="O265" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="266" spans="2:15">
@@ -13075,10 +13081,10 @@
         <v>341</v>
       </c>
       <c r="E266" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="I266" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="K266" t="s">
         <v>595</v>
@@ -13093,7 +13099,7 @@
         <v>341</v>
       </c>
       <c r="O266" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="267" spans="2:15">
@@ -13113,13 +13119,13 @@
         <v>585</v>
       </c>
       <c r="M267" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="N267" t="s">
         <v>342</v>
       </c>
       <c r="O267" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="268" spans="2:15">
@@ -13133,10 +13139,10 @@
         <v>343</v>
       </c>
       <c r="E268" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="I268" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="K268" t="s">
         <v>595</v>
@@ -13165,7 +13171,7 @@
         <v>344</v>
       </c>
       <c r="E269" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="K269" t="s">
         <v>596</v>
@@ -13174,7 +13180,7 @@
         <v>586</v>
       </c>
       <c r="M269" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="N269" t="s">
         <v>344</v>
@@ -13194,7 +13200,7 @@
         <v>345</v>
       </c>
       <c r="E270" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="K270" t="s">
         <v>595</v>
@@ -13203,13 +13209,13 @@
         <v>586</v>
       </c>
       <c r="M270" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="N270" t="s">
         <v>345</v>
       </c>
       <c r="O270" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="271" spans="2:15">
@@ -13223,22 +13229,22 @@
         <v>346</v>
       </c>
       <c r="E271" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="K271" t="s">
         <v>596</v>
       </c>
       <c r="L271" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="M271" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="N271" t="s">
         <v>346</v>
       </c>
       <c r="O271" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="272" spans="2:15">
@@ -13252,7 +13258,7 @@
         <v>347</v>
       </c>
       <c r="E272" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="K272" t="s">
         <v>595</v>
@@ -13261,13 +13267,13 @@
         <v>586</v>
       </c>
       <c r="M272" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="N272" t="s">
         <v>347</v>
       </c>
       <c r="O272" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="273" spans="2:15">
@@ -13281,7 +13287,7 @@
         <v>348</v>
       </c>
       <c r="E273" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="K273" t="s">
         <v>596</v>
@@ -13290,13 +13296,13 @@
         <v>587</v>
       </c>
       <c r="M273" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="N273" t="s">
         <v>348</v>
       </c>
       <c r="O273" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="274" spans="2:15">
@@ -13310,7 +13316,7 @@
         <v>349</v>
       </c>
       <c r="E274" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K274" t="s">
         <v>596</v>
@@ -13325,7 +13331,7 @@
         <v>349</v>
       </c>
       <c r="O274" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="275" spans="2:15">
@@ -13339,7 +13345,7 @@
         <v>350</v>
       </c>
       <c r="E275" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="K275" t="s">
         <v>595</v>
@@ -13348,13 +13354,13 @@
         <v>588</v>
       </c>
       <c r="M275" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="N275" t="s">
         <v>350</v>
       </c>
       <c r="O275" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="276" spans="2:15">
@@ -13368,7 +13374,7 @@
         <v>351</v>
       </c>
       <c r="E276" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="K276" t="s">
         <v>595</v>
@@ -13377,13 +13383,13 @@
         <v>585</v>
       </c>
       <c r="M276" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="N276" t="s">
         <v>351</v>
       </c>
       <c r="O276" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="277" spans="2:15">
@@ -13397,7 +13403,7 @@
         <v>352</v>
       </c>
       <c r="E277" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="K277" t="s">
         <v>595</v>
@@ -13406,7 +13412,7 @@
         <v>591</v>
       </c>
       <c r="M277" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="N277" t="s">
         <v>352</v>
@@ -13426,7 +13432,7 @@
         <v>353</v>
       </c>
       <c r="E278" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K278" t="s">
         <v>600</v>
@@ -13435,7 +13441,7 @@
         <v>594</v>
       </c>
       <c r="M278" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="N278" t="s">
         <v>353</v>
@@ -13455,7 +13461,7 @@
         <v>354</v>
       </c>
       <c r="E279" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K279" t="s">
         <v>596</v>
@@ -13484,7 +13490,7 @@
         <v>355</v>
       </c>
       <c r="E280" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="K280" t="s">
         <v>595</v>
@@ -13499,7 +13505,7 @@
         <v>355</v>
       </c>
       <c r="O280" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="281" spans="2:15">
@@ -13513,7 +13519,7 @@
         <v>356</v>
       </c>
       <c r="E281" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K281" t="s">
         <v>596</v>
@@ -13522,13 +13528,13 @@
         <v>583</v>
       </c>
       <c r="M281" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="N281" t="s">
         <v>356</v>
       </c>
       <c r="O281" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="282" spans="2:15">
@@ -13542,7 +13548,7 @@
         <v>357</v>
       </c>
       <c r="E282" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K282" t="s">
         <v>597</v>
@@ -13551,13 +13557,13 @@
         <v>20</v>
       </c>
       <c r="M282" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="N282" t="s">
         <v>357</v>
       </c>
       <c r="O282" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="283" spans="2:15">
@@ -13571,7 +13577,7 @@
         <v>358</v>
       </c>
       <c r="E283" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="K283" t="s">
         <v>597</v>
@@ -13580,7 +13586,7 @@
         <v>584</v>
       </c>
       <c r="M283" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="N283" t="s">
         <v>358</v>
@@ -13600,7 +13606,7 @@
         <v>359</v>
       </c>
       <c r="E284" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="K284" t="s">
         <v>595</v>
@@ -13615,7 +13621,7 @@
         <v>359</v>
       </c>
       <c r="O284" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="285" spans="2:15">
@@ -13629,7 +13635,7 @@
         <v>360</v>
       </c>
       <c r="E285" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="K285" t="s">
         <v>595</v>
@@ -13644,7 +13650,7 @@
         <v>360</v>
       </c>
       <c r="O285" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="286" spans="2:15">
@@ -13658,7 +13664,7 @@
         <v>361</v>
       </c>
       <c r="E286" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="K286" t="s">
         <v>596</v>
@@ -13673,7 +13679,7 @@
         <v>361</v>
       </c>
       <c r="O286" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="287" spans="2:15">
@@ -13687,7 +13693,7 @@
         <v>362</v>
       </c>
       <c r="E287" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K287" t="s">
         <v>595</v>
@@ -13702,7 +13708,7 @@
         <v>362</v>
       </c>
       <c r="O287" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="288" spans="2:15">
@@ -13716,7 +13722,7 @@
         <v>363</v>
       </c>
       <c r="E288" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="K288" t="s">
         <v>596</v>
@@ -13745,7 +13751,7 @@
         <v>364</v>
       </c>
       <c r="E289" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="K289" t="s">
         <v>595</v>
@@ -13754,7 +13760,7 @@
         <v>585</v>
       </c>
       <c r="M289" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N289" t="s">
         <v>364</v>
@@ -13774,7 +13780,7 @@
         <v>365</v>
       </c>
       <c r="E290" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="K290" t="s">
         <v>595</v>
@@ -13803,7 +13809,7 @@
         <v>366</v>
       </c>
       <c r="E291" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="K291" t="s">
         <v>595</v>
@@ -13812,7 +13818,7 @@
         <v>589</v>
       </c>
       <c r="M291" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="N291" t="s">
         <v>366</v>
@@ -13832,7 +13838,7 @@
         <v>367</v>
       </c>
       <c r="E292" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="K292" t="s">
         <v>596</v>
@@ -13847,7 +13853,7 @@
         <v>367</v>
       </c>
       <c r="O292" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="293" spans="2:15">
@@ -13861,7 +13867,7 @@
         <v>368</v>
       </c>
       <c r="E293" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="K293" t="s">
         <v>595</v>
@@ -13876,7 +13882,7 @@
         <v>368</v>
       </c>
       <c r="O293" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="294" spans="2:15">
@@ -13890,7 +13896,7 @@
         <v>369</v>
       </c>
       <c r="E294" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="K294" t="s">
         <v>596</v>
@@ -13899,13 +13905,13 @@
         <v>588</v>
       </c>
       <c r="M294" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="N294" t="s">
         <v>369</v>
       </c>
       <c r="O294" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="295" spans="2:15">
@@ -13919,7 +13925,7 @@
         <v>370</v>
       </c>
       <c r="E295" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K295" t="s">
         <v>596</v>
@@ -13928,13 +13934,13 @@
         <v>588</v>
       </c>
       <c r="M295" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="N295" t="s">
         <v>370</v>
       </c>
       <c r="O295" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="296" spans="2:15">
@@ -13948,7 +13954,7 @@
         <v>371</v>
       </c>
       <c r="E296" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="K296" t="s">
         <v>595</v>
@@ -13957,7 +13963,7 @@
         <v>585</v>
       </c>
       <c r="M296" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="N296" t="s">
         <v>371</v>
@@ -13977,7 +13983,7 @@
         <v>372</v>
       </c>
       <c r="E297" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="K297" t="s">
         <v>595</v>
@@ -13992,7 +13998,7 @@
         <v>372</v>
       </c>
       <c r="O297" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="298" spans="2:15">
@@ -14006,7 +14012,7 @@
         <v>373</v>
       </c>
       <c r="E298" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="K298" t="s">
         <v>596</v>
@@ -14015,13 +14021,13 @@
         <v>20</v>
       </c>
       <c r="M298" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="N298" t="s">
         <v>373</v>
       </c>
       <c r="O298" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="299" spans="2:15">
@@ -14035,7 +14041,7 @@
         <v>374</v>
       </c>
       <c r="E299" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="K299" t="s">
         <v>595</v>
@@ -14044,13 +14050,13 @@
         <v>592</v>
       </c>
       <c r="M299" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="N299" t="s">
         <v>374</v>
       </c>
       <c r="O299" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="300" spans="2:15">
@@ -14064,7 +14070,7 @@
         <v>375</v>
       </c>
       <c r="E300" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K300" t="s">
         <v>595</v>
@@ -14093,7 +14099,7 @@
         <v>376</v>
       </c>
       <c r="E301" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="K301" t="s">
         <v>595</v>
@@ -14102,7 +14108,7 @@
         <v>585</v>
       </c>
       <c r="M301" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N301" t="s">
         <v>376</v>
@@ -14122,7 +14128,7 @@
         <v>377</v>
       </c>
       <c r="E302" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="K302" t="s">
         <v>595</v>
@@ -14131,13 +14137,13 @@
         <v>585</v>
       </c>
       <c r="M302" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="N302" t="s">
         <v>377</v>
       </c>
       <c r="O302" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="303" spans="2:15">
@@ -14151,7 +14157,7 @@
         <v>378</v>
       </c>
       <c r="E303" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="K303" t="s">
         <v>591</v>
@@ -14160,13 +14166,13 @@
         <v>591</v>
       </c>
       <c r="M303" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="N303" t="s">
         <v>378</v>
       </c>
       <c r="O303" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="304" spans="2:15">
@@ -14180,7 +14186,7 @@
         <v>379</v>
       </c>
       <c r="E304" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="K304" t="s">
         <v>596</v>
@@ -14189,13 +14195,13 @@
         <v>588</v>
       </c>
       <c r="M304" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="N304" t="s">
         <v>379</v>
       </c>
       <c r="O304" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="305" spans="1:15">
@@ -14209,7 +14215,7 @@
         <v>380</v>
       </c>
       <c r="E305" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K305" t="s">
         <v>596</v>
@@ -14218,13 +14224,13 @@
         <v>588</v>
       </c>
       <c r="M305" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="N305" t="s">
         <v>380</v>
       </c>
       <c r="O305" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="306" spans="1:15">
@@ -14238,7 +14244,7 @@
         <v>381</v>
       </c>
       <c r="E306" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="K306" t="s">
         <v>600</v>
@@ -14267,7 +14273,7 @@
         <v>382</v>
       </c>
       <c r="E307" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="K307" t="s">
         <v>596</v>
@@ -14276,13 +14282,13 @@
         <v>20</v>
       </c>
       <c r="M307" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="N307" t="s">
         <v>382</v>
       </c>
       <c r="O307" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="308" spans="1:15">
@@ -14296,7 +14302,7 @@
         <v>383</v>
       </c>
       <c r="E308" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="K308" t="s">
         <v>595</v>
@@ -14311,7 +14317,7 @@
         <v>383</v>
       </c>
       <c r="O308" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="309" spans="1:15">
@@ -14325,7 +14331,7 @@
         <v>384</v>
       </c>
       <c r="E309" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="K309" t="s">
         <v>596</v>
@@ -14334,13 +14340,13 @@
         <v>590</v>
       </c>
       <c r="M309" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="N309" t="s">
         <v>384</v>
       </c>
       <c r="O309" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="310" spans="1:15">
@@ -14368,7 +14374,7 @@
         <v>35</v>
       </c>
       <c r="E311" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="312" spans="1:15">
@@ -14382,7 +14388,7 @@
         <v>385</v>
       </c>
       <c r="E312" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="313" spans="1:15">
@@ -14396,7 +14402,7 @@
         <v>386</v>
       </c>
       <c r="E313" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="314" spans="1:15">
@@ -14410,7 +14416,7 @@
         <v>387</v>
       </c>
       <c r="E314" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="315" spans="1:15">
@@ -14424,7 +14430,7 @@
         <v>388</v>
       </c>
       <c r="E315" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="316" spans="1:15">
@@ -14438,7 +14444,7 @@
         <v>389</v>
       </c>
       <c r="E316" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="317" spans="1:15">
@@ -14452,7 +14458,7 @@
         <v>390</v>
       </c>
       <c r="E317" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="318" spans="1:15">
@@ -14466,7 +14472,7 @@
         <v>391</v>
       </c>
       <c r="E318" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="319" spans="1:15">
@@ -14480,7 +14486,7 @@
         <v>392</v>
       </c>
       <c r="E319" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="320" spans="1:15">
@@ -14494,7 +14500,7 @@
         <v>393</v>
       </c>
       <c r="E320" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -14508,7 +14514,7 @@
         <v>394</v>
       </c>
       <c r="E321" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -14522,7 +14528,7 @@
         <v>395</v>
       </c>
       <c r="E322" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -14536,7 +14542,7 @@
         <v>396</v>
       </c>
       <c r="E323" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -14550,7 +14556,7 @@
         <v>397</v>
       </c>
       <c r="E324" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -14564,7 +14570,7 @@
         <v>398</v>
       </c>
       <c r="E325" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -14578,7 +14584,7 @@
         <v>399</v>
       </c>
       <c r="E326" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -14592,7 +14598,7 @@
         <v>400</v>
       </c>
       <c r="E327" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -14606,7 +14612,7 @@
         <v>401</v>
       </c>
       <c r="E328" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -14620,7 +14626,7 @@
         <v>402</v>
       </c>
       <c r="E329" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -14634,7 +14640,7 @@
         <v>403</v>
       </c>
       <c r="E330" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -14648,7 +14654,7 @@
         <v>404</v>
       </c>
       <c r="E331" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -14676,7 +14682,7 @@
         <v>405</v>
       </c>
       <c r="E333" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -14690,7 +14696,7 @@
         <v>406</v>
       </c>
       <c r="E334" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -14704,7 +14710,7 @@
         <v>407</v>
       </c>
       <c r="E335" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -14718,7 +14724,7 @@
         <v>408</v>
       </c>
       <c r="E336" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -14732,7 +14738,7 @@
         <v>409</v>
       </c>
       <c r="E337" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -14746,7 +14752,7 @@
         <v>410</v>
       </c>
       <c r="E338" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -14763,7 +14769,7 @@
         <v>411</v>
       </c>
       <c r="E339" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -14780,7 +14786,7 @@
         <v>412</v>
       </c>
       <c r="E340" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -14797,7 +14803,7 @@
         <v>413</v>
       </c>
       <c r="E341" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -14814,7 +14820,7 @@
         <v>414</v>
       </c>
       <c r="E342" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -14845,7 +14851,7 @@
         <v>415</v>
       </c>
       <c r="E344" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -14862,7 +14868,7 @@
         <v>416</v>
       </c>
       <c r="E345" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -14879,7 +14885,7 @@
         <v>417</v>
       </c>
       <c r="E346" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -14896,7 +14902,7 @@
         <v>418</v>
       </c>
       <c r="E347" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -14955,7 +14961,7 @@
         <v>422</v>
       </c>
       <c r="E351" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -14997,7 +15003,7 @@
         <v>424</v>
       </c>
       <c r="E354" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -15011,7 +15017,7 @@
         <v>425</v>
       </c>
       <c r="E355" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -15025,7 +15031,7 @@
         <v>426</v>
       </c>
       <c r="E356" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -15039,7 +15045,7 @@
         <v>427</v>
       </c>
       <c r="E357" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -15053,7 +15059,7 @@
         <v>428</v>
       </c>
       <c r="E358" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -15067,7 +15073,7 @@
         <v>429</v>
       </c>
       <c r="E359" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -15081,7 +15087,7 @@
         <v>430</v>
       </c>
       <c r="E360" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -15095,7 +15101,7 @@
         <v>431</v>
       </c>
       <c r="E361" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -15109,7 +15115,7 @@
         <v>432</v>
       </c>
       <c r="E362" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -15168,7 +15174,7 @@
         <v>433</v>
       </c>
       <c r="E366" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -15185,7 +15191,7 @@
         <v>434</v>
       </c>
       <c r="E367" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -15216,7 +15222,7 @@
         <v>435</v>
       </c>
       <c r="E369" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -15289,7 +15295,7 @@
         <v>438</v>
       </c>
       <c r="E374" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -15317,7 +15323,7 @@
         <v>439</v>
       </c>
       <c r="E376" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -15331,7 +15337,7 @@
         <v>440</v>
       </c>
       <c r="E377" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -15345,7 +15351,7 @@
         <v>441</v>
       </c>
       <c r="E378" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -15359,7 +15365,7 @@
         <v>442</v>
       </c>
       <c r="E379" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -15373,7 +15379,7 @@
         <v>443</v>
       </c>
       <c r="E380" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -15387,7 +15393,7 @@
         <v>444</v>
       </c>
       <c r="E381" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -15401,7 +15407,7 @@
         <v>445</v>
       </c>
       <c r="E382" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -15415,7 +15421,7 @@
         <v>446</v>
       </c>
       <c r="E383" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -15429,7 +15435,7 @@
         <v>447</v>
       </c>
       <c r="E384" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="385" spans="2:5">
@@ -15443,7 +15449,7 @@
         <v>448</v>
       </c>
       <c r="E385" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="386" spans="2:5">
@@ -15600,7 +15606,7 @@
         <v>462</v>
       </c>
       <c r="E399" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="400" spans="2:5">
@@ -15614,7 +15620,7 @@
         <v>463</v>
       </c>
       <c r="E400" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -15686,7 +15692,7 @@
         <v>84</v>
       </c>
       <c r="E406" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -15700,7 +15706,7 @@
         <v>469</v>
       </c>
       <c r="E407" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -15714,7 +15720,7 @@
         <v>470</v>
       </c>
       <c r="E408" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -15772,7 +15778,7 @@
         <v>475</v>
       </c>
       <c r="E413" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -15786,7 +15792,7 @@
         <v>476</v>
       </c>
       <c r="E414" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -15800,7 +15806,7 @@
         <v>477</v>
       </c>
       <c r="E415" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -15814,7 +15820,7 @@
         <v>478</v>
       </c>
       <c r="E416" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -15828,7 +15834,7 @@
         <v>479</v>
       </c>
       <c r="E417" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -15842,7 +15848,7 @@
         <v>480</v>
       </c>
       <c r="E418" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -15859,7 +15865,7 @@
         <v>411</v>
       </c>
       <c r="E419" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -15876,7 +15882,7 @@
         <v>481</v>
       </c>
       <c r="E420" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -15893,7 +15899,7 @@
         <v>482</v>
       </c>
       <c r="E421" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -15910,7 +15916,7 @@
         <v>483</v>
       </c>
       <c r="E422" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -15927,7 +15933,7 @@
         <v>484</v>
       </c>
       <c r="E423" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -15944,7 +15950,7 @@
         <v>485</v>
       </c>
       <c r="E424" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -15961,7 +15967,7 @@
         <v>486</v>
       </c>
       <c r="E425" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -15978,7 +15984,7 @@
         <v>487</v>
       </c>
       <c r="E426" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -16009,7 +16015,7 @@
         <v>488</v>
       </c>
       <c r="E428" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -16026,7 +16032,7 @@
         <v>489</v>
       </c>
       <c r="E429" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -16043,7 +16049,7 @@
         <v>490</v>
       </c>
       <c r="E430" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -16060,7 +16066,7 @@
         <v>491</v>
       </c>
       <c r="E431" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -16077,7 +16083,7 @@
         <v>411</v>
       </c>
       <c r="E432" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -16094,7 +16100,7 @@
         <v>492</v>
       </c>
       <c r="E433" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -16111,7 +16117,7 @@
         <v>493</v>
       </c>
       <c r="E434" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -16128,7 +16134,7 @@
         <v>411</v>
       </c>
       <c r="E435" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -16145,7 +16151,7 @@
         <v>494</v>
       </c>
       <c r="E436" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -16176,7 +16182,7 @@
         <v>496</v>
       </c>
       <c r="E438" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -16193,7 +16199,7 @@
         <v>497</v>
       </c>
       <c r="E439" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -16210,7 +16216,7 @@
         <v>498</v>
       </c>
       <c r="E440" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -16227,7 +16233,7 @@
         <v>499</v>
       </c>
       <c r="E441" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -16244,7 +16250,7 @@
         <v>500</v>
       </c>
       <c r="E442" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -16261,7 +16267,7 @@
         <v>501</v>
       </c>
       <c r="E443" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -16278,7 +16284,7 @@
         <v>502</v>
       </c>
       <c r="E444" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -16295,7 +16301,7 @@
         <v>411</v>
       </c>
       <c r="E445" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -16312,7 +16318,7 @@
         <v>503</v>
       </c>
       <c r="E446" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -16329,7 +16335,7 @@
         <v>504</v>
       </c>
       <c r="E447" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -16346,7 +16352,7 @@
         <v>505</v>
       </c>
       <c r="E448" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -16405,7 +16411,7 @@
         <v>506</v>
       </c>
       <c r="E452" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -16422,7 +16428,7 @@
         <v>507</v>
       </c>
       <c r="E453" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -16439,7 +16445,7 @@
         <v>508</v>
       </c>
       <c r="E454" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -16456,7 +16462,7 @@
         <v>509</v>
       </c>
       <c r="E455" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -16487,7 +16493,7 @@
         <v>511</v>
       </c>
       <c r="E457" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -16504,7 +16510,7 @@
         <v>512</v>
       </c>
       <c r="E458" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -16521,7 +16527,7 @@
         <v>513</v>
       </c>
       <c r="E459" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -16538,7 +16544,7 @@
         <v>514</v>
       </c>
       <c r="E460" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -16555,7 +16561,7 @@
         <v>515</v>
       </c>
       <c r="E461" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -16572,7 +16578,7 @@
         <v>516</v>
       </c>
       <c r="E462" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -16589,7 +16595,7 @@
         <v>517</v>
       </c>
       <c r="E463" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -16606,7 +16612,7 @@
         <v>518</v>
       </c>
       <c r="E464" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -16623,7 +16629,7 @@
         <v>411</v>
       </c>
       <c r="E465" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -16640,7 +16646,7 @@
         <v>519</v>
       </c>
       <c r="E466" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -16657,7 +16663,7 @@
         <v>520</v>
       </c>
       <c r="E467" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -16674,7 +16680,7 @@
         <v>521</v>
       </c>
       <c r="E468" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -16705,7 +16711,7 @@
         <v>411</v>
       </c>
       <c r="E470" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -16722,7 +16728,7 @@
         <v>518</v>
       </c>
       <c r="E471" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -16739,7 +16745,7 @@
         <v>522</v>
       </c>
       <c r="E472" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -16770,7 +16776,7 @@
         <v>411</v>
       </c>
       <c r="E474" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -16787,7 +16793,7 @@
         <v>523</v>
       </c>
       <c r="E475" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -16804,7 +16810,7 @@
         <v>524</v>
       </c>
       <c r="E476" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -16821,7 +16827,7 @@
         <v>525</v>
       </c>
       <c r="E477" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -16838,7 +16844,7 @@
         <v>526</v>
       </c>
       <c r="E478" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -16855,7 +16861,7 @@
         <v>527</v>
       </c>
       <c r="E479" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -16872,7 +16878,7 @@
         <v>411</v>
       </c>
       <c r="E480" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -16889,7 +16895,7 @@
         <v>528</v>
       </c>
       <c r="E481" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -16906,7 +16912,7 @@
         <v>529</v>
       </c>
       <c r="E482" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -16923,7 +16929,7 @@
         <v>530</v>
       </c>
       <c r="E483" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -16940,7 +16946,7 @@
         <v>531</v>
       </c>
       <c r="E484" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -16957,7 +16963,7 @@
         <v>532</v>
       </c>
       <c r="E485" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -16974,7 +16980,7 @@
         <v>533</v>
       </c>
       <c r="E486" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -16991,7 +16997,7 @@
         <v>534</v>
       </c>
       <c r="E487" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -17008,7 +17014,7 @@
         <v>535</v>
       </c>
       <c r="E488" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -17025,7 +17031,7 @@
         <v>536</v>
       </c>
       <c r="E489" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -17042,7 +17048,7 @@
         <v>537</v>
       </c>
       <c r="E490" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -17059,7 +17065,7 @@
         <v>538</v>
       </c>
       <c r="E491" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -17076,7 +17082,7 @@
         <v>539</v>
       </c>
       <c r="E492" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -17093,7 +17099,7 @@
         <v>411</v>
       </c>
       <c r="E493" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -17110,7 +17116,7 @@
         <v>540</v>
       </c>
       <c r="E494" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -17127,7 +17133,7 @@
         <v>541</v>
       </c>
       <c r="E495" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -17144,7 +17150,7 @@
         <v>542</v>
       </c>
       <c r="E496" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -17205,7 +17211,7 @@
         <v>15</v>
       </c>
       <c r="E501" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="502" spans="1:5">
@@ -17230,7 +17236,7 @@
         <v>41</v>
       </c>
       <c r="E503" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="504" spans="1:5">
@@ -17255,7 +17261,7 @@
         <v>548</v>
       </c>
       <c r="E505" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -17283,7 +17289,7 @@
         <v>4</v>
       </c>
       <c r="E507" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="508" spans="1:5">
@@ -17297,7 +17303,7 @@
         <v>549</v>
       </c>
       <c r="E508" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -17311,7 +17317,7 @@
         <v>550</v>
       </c>
       <c r="E509" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -17325,7 +17331,7 @@
         <v>551</v>
       </c>
       <c r="E510" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -17339,7 +17345,7 @@
         <v>552</v>
       </c>
       <c r="E511" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="512" spans="1:5">
@@ -17370,7 +17376,7 @@
         <v>553</v>
       </c>
       <c r="E513" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -17387,7 +17393,7 @@
         <v>554</v>
       </c>
       <c r="E514" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="515" spans="1:5">
@@ -17404,7 +17410,7 @@
         <v>555</v>
       </c>
       <c r="E515" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -17421,7 +17427,7 @@
         <v>556</v>
       </c>
       <c r="E516" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="517" spans="1:5">
@@ -17438,7 +17444,7 @@
         <v>557</v>
       </c>
       <c r="E517" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="518" spans="1:5">
@@ -17455,7 +17461,7 @@
         <v>411</v>
       </c>
       <c r="E518" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="519" spans="1:5">
@@ -17570,7 +17576,7 @@
         <v>411</v>
       </c>
       <c r="E526" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="527" spans="1:5">
@@ -17587,7 +17593,7 @@
         <v>564</v>
       </c>
       <c r="E527" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="528" spans="1:5">
@@ -17604,7 +17610,7 @@
         <v>565</v>
       </c>
       <c r="E528" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="529" spans="1:5">
@@ -17621,7 +17627,7 @@
         <v>566</v>
       </c>
       <c r="E529" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="530" spans="1:5">
@@ -17638,7 +17644,7 @@
         <v>567</v>
       </c>
       <c r="E530" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="531" spans="1:5">
@@ -17666,7 +17672,7 @@
         <v>568</v>
       </c>
       <c r="E532" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="533" spans="1:5">
@@ -17680,7 +17686,7 @@
         <v>569</v>
       </c>
       <c r="E533" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="534" spans="1:5">
@@ -17694,7 +17700,7 @@
         <v>570</v>
       </c>
       <c r="E534" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="535" spans="1:5">
@@ -17708,7 +17714,7 @@
         <v>571</v>
       </c>
       <c r="E535" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="536" spans="1:5">
@@ -17722,7 +17728,7 @@
         <v>572</v>
       </c>
       <c r="E536" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="537" spans="1:5">
@@ -17736,7 +17742,7 @@
         <v>573</v>
       </c>
       <c r="E537" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="538" spans="1:5">
@@ -17750,7 +17756,7 @@
         <v>574</v>
       </c>
       <c r="E538" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="539" spans="1:5">
@@ -17764,7 +17770,7 @@
         <v>575</v>
       </c>
       <c r="E539" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="540" spans="1:5">
@@ -17778,7 +17784,7 @@
         <v>576</v>
       </c>
       <c r="E540" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="541" spans="1:5">
@@ -17792,7 +17798,7 @@
         <v>577</v>
       </c>
       <c r="E541" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="542" spans="1:5">
@@ -17806,7 +17812,7 @@
         <v>578</v>
       </c>
       <c r="E542" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="543" spans="1:5">
@@ -17820,7 +17826,7 @@
         <v>579</v>
       </c>
       <c r="E543" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -17834,7 +17840,7 @@
         <v>580</v>
       </c>
       <c r="E544" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="545" spans="1:5">
@@ -17848,7 +17854,7 @@
         <v>581</v>
       </c>
       <c r="E545" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="546" spans="1:5">
@@ -17862,7 +17868,7 @@
         <v>582</v>
       </c>
       <c r="E546" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="547" spans="1:5">
@@ -17890,7 +17896,7 @@
         <v>583</v>
       </c>
       <c r="E548" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="549" spans="1:5">
@@ -17904,7 +17910,7 @@
         <v>584</v>
       </c>
       <c r="E549" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="550" spans="1:5">
@@ -17918,7 +17924,7 @@
         <v>20</v>
       </c>
       <c r="E550" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -17932,7 +17938,7 @@
         <v>585</v>
       </c>
       <c r="E551" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="552" spans="1:5">
@@ -17946,7 +17952,7 @@
         <v>586</v>
       </c>
       <c r="E552" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="553" spans="1:5">
@@ -17960,7 +17966,7 @@
         <v>587</v>
       </c>
       <c r="E553" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="554" spans="1:5">
@@ -17974,7 +17980,7 @@
         <v>588</v>
       </c>
       <c r="E554" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="555" spans="1:5">
@@ -17988,7 +17994,7 @@
         <v>589</v>
       </c>
       <c r="E555" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="556" spans="1:5">
@@ -18024,7 +18030,7 @@
         <v>592</v>
       </c>
       <c r="E558" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="559" spans="1:5">
@@ -18038,7 +18044,7 @@
         <v>593</v>
       </c>
       <c r="E559" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -18052,7 +18058,7 @@
         <v>594</v>
       </c>
       <c r="E560" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -18080,7 +18086,7 @@
         <v>595</v>
       </c>
       <c r="E562" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -18094,7 +18100,7 @@
         <v>596</v>
       </c>
       <c r="E563" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -18108,7 +18114,7 @@
         <v>597</v>
       </c>
       <c r="E564" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="565" spans="1:5">
@@ -18122,7 +18128,7 @@
         <v>598</v>
       </c>
       <c r="E565" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="566" spans="1:5">
@@ -18136,7 +18142,7 @@
         <v>599</v>
       </c>
       <c r="E566" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="567" spans="1:5">
@@ -18150,7 +18156,7 @@
         <v>600</v>
       </c>
       <c r="E567" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -18164,7 +18170,7 @@
         <v>601</v>
       </c>
       <c r="E568" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -18178,7 +18184,7 @@
         <v>602</v>
       </c>
       <c r="E569" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="570" spans="1:5">
@@ -18192,7 +18198,7 @@
         <v>603</v>
       </c>
       <c r="E570" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="571" spans="1:5">
@@ -18206,7 +18212,7 @@
         <v>604</v>
       </c>
       <c r="E571" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -18220,7 +18226,7 @@
         <v>605</v>
       </c>
       <c r="E572" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="573" spans="1:5">
@@ -18237,7 +18243,7 @@
         <v>411</v>
       </c>
       <c r="E573" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -18492,7 +18498,7 @@
         <v>78</v>
       </c>
       <c r="E591" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -18506,7 +18512,7 @@
         <v>10</v>
       </c>
       <c r="E592" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="593" spans="1:5">
@@ -18520,7 +18526,7 @@
         <v>11</v>
       </c>
       <c r="E593" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="594" spans="1:5">
@@ -18534,7 +18540,7 @@
         <v>22</v>
       </c>
       <c r="E594" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="595" spans="1:5">
@@ -18548,7 +18554,7 @@
         <v>13</v>
       </c>
       <c r="E595" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="596" spans="1:5">
@@ -18562,7 +18568,7 @@
         <v>14</v>
       </c>
       <c r="E596" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -18579,7 +18585,7 @@
         <v>411</v>
       </c>
       <c r="E597" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="598" spans="1:5">
@@ -18610,7 +18616,7 @@
         <v>607</v>
       </c>
       <c r="E599" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="600" spans="1:5">
@@ -18627,7 +18633,7 @@
         <v>608</v>
       </c>
       <c r="E600" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="601" spans="1:5">
@@ -18644,7 +18650,7 @@
         <v>609</v>
       </c>
       <c r="E601" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="602" spans="1:5">
@@ -18661,7 +18667,7 @@
         <v>411</v>
       </c>
       <c r="E602" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="603" spans="1:5">
@@ -18678,7 +18684,7 @@
         <v>610</v>
       </c>
       <c r="E603" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -18695,7 +18701,7 @@
         <v>611</v>
       </c>
       <c r="E604" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="605" spans="1:5">
@@ -18712,7 +18718,7 @@
         <v>612</v>
       </c>
       <c r="E605" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -18729,7 +18735,7 @@
         <v>411</v>
       </c>
       <c r="E606" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="607" spans="1:5">
@@ -18746,7 +18752,7 @@
         <v>613</v>
       </c>
       <c r="E607" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="608" spans="1:5">
@@ -18763,7 +18769,7 @@
         <v>614</v>
       </c>
       <c r="E608" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="609" spans="1:5">
@@ -18780,7 +18786,7 @@
         <v>615</v>
       </c>
       <c r="E609" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="610" spans="1:5">
@@ -18797,7 +18803,7 @@
         <v>411</v>
       </c>
       <c r="E610" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="611" spans="1:5">
@@ -18828,7 +18834,7 @@
         <v>617</v>
       </c>
       <c r="E612" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="613" spans="1:5">
@@ -18845,7 +18851,7 @@
         <v>618</v>
       </c>
       <c r="E613" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="614" spans="1:5">
@@ -18862,7 +18868,7 @@
         <v>619</v>
       </c>
       <c r="E614" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="615" spans="1:5">
@@ -18879,7 +18885,7 @@
         <v>620</v>
       </c>
       <c r="E615" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="616" spans="1:5">
@@ -18896,7 +18902,7 @@
         <v>621</v>
       </c>
       <c r="E616" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="617" spans="1:5">
@@ -18913,7 +18919,7 @@
         <v>622</v>
       </c>
       <c r="E617" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="618" spans="1:5">
@@ -18930,7 +18936,7 @@
         <v>623</v>
       </c>
       <c r="E618" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -18947,7 +18953,7 @@
         <v>624</v>
       </c>
       <c r="E619" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -18964,7 +18970,7 @@
         <v>625</v>
       </c>
       <c r="E620" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -18981,7 +18987,7 @@
         <v>626</v>
       </c>
       <c r="E621" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -18998,7 +19004,7 @@
         <v>627</v>
       </c>
       <c r="E622" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="623" spans="1:5">
@@ -19015,7 +19021,7 @@
         <v>628</v>
       </c>
       <c r="E623" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -19032,7 +19038,7 @@
         <v>629</v>
       </c>
       <c r="E624" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -19049,7 +19055,7 @@
         <v>630</v>
       </c>
       <c r="E625" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -19066,7 +19072,7 @@
         <v>631</v>
       </c>
       <c r="E626" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -19083,7 +19089,7 @@
         <v>632</v>
       </c>
       <c r="E627" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -19100,7 +19106,7 @@
         <v>633</v>
       </c>
       <c r="E628" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -19117,7 +19123,7 @@
         <v>634</v>
       </c>
       <c r="E629" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="630" spans="1:5">
@@ -19134,7 +19140,7 @@
         <v>635</v>
       </c>
       <c r="E630" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -19151,7 +19157,7 @@
         <v>636</v>
       </c>
       <c r="E631" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -19168,7 +19174,7 @@
         <v>637</v>
       </c>
       <c r="E632" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="633" spans="1:5">
@@ -19185,7 +19191,7 @@
         <v>638</v>
       </c>
       <c r="E633" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -19202,7 +19208,7 @@
         <v>639</v>
       </c>
       <c r="E634" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -19241,7 +19247,7 @@
         <v>640</v>
       </c>
       <c r="E637" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -19255,7 +19261,7 @@
         <v>641</v>
       </c>
       <c r="E638" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -19269,7 +19275,7 @@
         <v>642</v>
       </c>
       <c r="E639" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -19283,7 +19289,7 @@
         <v>643</v>
       </c>
       <c r="E640" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="641" spans="1:5">
@@ -19297,7 +19303,7 @@
         <v>644</v>
       </c>
       <c r="E641" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -19311,7 +19317,7 @@
         <v>645</v>
       </c>
       <c r="E642" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="643" spans="1:5">
@@ -19325,7 +19331,7 @@
         <v>646</v>
       </c>
       <c r="E643" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -19353,7 +19359,7 @@
         <v>1</v>
       </c>
       <c r="E645" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="646" spans="1:5">
@@ -19367,7 +19373,7 @@
         <v>2</v>
       </c>
       <c r="E646" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="647" spans="1:5">
@@ -19381,7 +19387,7 @@
         <v>3</v>
       </c>
       <c r="E647" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -19395,7 +19401,7 @@
         <v>4</v>
       </c>
       <c r="E648" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="649" spans="1:5">
@@ -19426,7 +19432,7 @@
         <v>647</v>
       </c>
       <c r="E650" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="651" spans="1:5">
@@ -19443,7 +19449,7 @@
         <v>648</v>
       </c>
       <c r="E651" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="652" spans="1:5">
@@ -19460,7 +19466,7 @@
         <v>649</v>
       </c>
       <c r="E652" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -19477,7 +19483,7 @@
         <v>650</v>
       </c>
       <c r="E653" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="654" spans="1:5">
@@ -19494,7 +19500,7 @@
         <v>651</v>
       </c>
       <c r="E654" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -19511,7 +19517,7 @@
         <v>652</v>
       </c>
       <c r="E655" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="656" spans="1:5">
@@ -19525,7 +19531,7 @@
         <v>653</v>
       </c>
       <c r="E656" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -19539,7 +19545,7 @@
         <v>654</v>
       </c>
       <c r="E657" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -19553,7 +19559,7 @@
         <v>655</v>
       </c>
       <c r="E658" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -19570,7 +19576,7 @@
         <v>411</v>
       </c>
       <c r="E659" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="660" spans="1:5">
@@ -19587,7 +19593,7 @@
         <v>656</v>
       </c>
       <c r="E660" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -19604,7 +19610,7 @@
         <v>657</v>
       </c>
       <c r="E661" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="662" spans="1:5">
@@ -19621,7 +19627,7 @@
         <v>658</v>
       </c>
       <c r="E662" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="663" spans="1:5">
@@ -19638,7 +19644,7 @@
         <v>659</v>
       </c>
       <c r="E663" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -19655,7 +19661,7 @@
         <v>660</v>
       </c>
       <c r="E664" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -19672,7 +19678,7 @@
         <v>661</v>
       </c>
       <c r="E665" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -19689,7 +19695,7 @@
         <v>662</v>
       </c>
       <c r="E666" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="667" spans="1:5">
@@ -19706,7 +19712,7 @@
         <v>663</v>
       </c>
       <c r="E667" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -19723,7 +19729,7 @@
         <v>664</v>
       </c>
       <c r="E668" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -19740,7 +19746,7 @@
         <v>665</v>
       </c>
       <c r="E669" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="670" spans="1:5">
@@ -19757,7 +19763,7 @@
         <v>411</v>
       </c>
       <c r="E670" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -19774,7 +19780,7 @@
         <v>666</v>
       </c>
       <c r="E671" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="672" spans="1:5">
@@ -19791,7 +19797,7 @@
         <v>667</v>
       </c>
       <c r="E672" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -19878,7 +19884,7 @@
         <v>672</v>
       </c>
       <c r="E678" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="679" spans="1:5">
@@ -19895,7 +19901,7 @@
         <v>673</v>
       </c>
       <c r="E679" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="680" spans="1:5">
@@ -19912,7 +19918,7 @@
         <v>674</v>
       </c>
       <c r="E680" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="681" spans="1:5">
@@ -19943,7 +19949,7 @@
         <v>675</v>
       </c>
       <c r="E682" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="683" spans="1:5">
@@ -19960,7 +19966,7 @@
         <v>676</v>
       </c>
       <c r="E683" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="684" spans="1:5">
@@ -19977,7 +19983,7 @@
         <v>677</v>
       </c>
       <c r="E684" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="685" spans="1:5">
@@ -19994,7 +20000,7 @@
         <v>678</v>
       </c>
       <c r="E685" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="686" spans="1:5">
@@ -20011,7 +20017,7 @@
         <v>679</v>
       </c>
       <c r="E686" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="687" spans="1:5">
@@ -20028,7 +20034,7 @@
         <v>680</v>
       </c>
       <c r="E687" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="688" spans="1:5">
@@ -20045,7 +20051,7 @@
         <v>681</v>
       </c>
       <c r="E688" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="689" spans="1:5">
@@ -20062,7 +20068,7 @@
         <v>682</v>
       </c>
       <c r="E689" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="690" spans="1:5">
@@ -20079,7 +20085,7 @@
         <v>683</v>
       </c>
       <c r="E690" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="691" spans="1:5">
@@ -20247,7 +20253,7 @@
         <v>690</v>
       </c>
       <c r="E702" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="703" spans="1:5">
@@ -20261,7 +20267,7 @@
         <v>691</v>
       </c>
       <c r="E703" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="704" spans="1:5">
@@ -20275,7 +20281,7 @@
         <v>692</v>
       </c>
       <c r="E704" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="705" spans="1:6">
@@ -20289,7 +20295,7 @@
         <v>693</v>
       </c>
       <c r="E705" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="706" spans="1:6">
@@ -20303,7 +20309,7 @@
         <v>694</v>
       </c>
       <c r="E706" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="707" spans="1:6">
@@ -20317,7 +20323,7 @@
         <v>695</v>
       </c>
       <c r="E707" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="708" spans="1:6">
@@ -20331,7 +20337,7 @@
         <v>696</v>
       </c>
       <c r="E708" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="709" spans="1:6">
@@ -20345,10 +20351,10 @@
         <v>697</v>
       </c>
       <c r="E709" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F709" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="710" spans="1:6">
@@ -20376,7 +20382,7 @@
         <v>78</v>
       </c>
       <c r="E711" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -20390,7 +20396,7 @@
         <v>698</v>
       </c>
       <c r="E712" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="713" spans="1:6">
@@ -20404,7 +20410,7 @@
         <v>699</v>
       </c>
       <c r="E713" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="714" spans="1:6">
@@ -20418,7 +20424,7 @@
         <v>700</v>
       </c>
       <c r="E714" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="715" spans="1:6">
@@ -20432,7 +20438,7 @@
         <v>701</v>
       </c>
       <c r="E715" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="716" spans="1:6">
@@ -20446,7 +20452,7 @@
         <v>702</v>
       </c>
       <c r="E716" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="717" spans="1:6">
@@ -20460,7 +20466,7 @@
         <v>703</v>
       </c>
       <c r="E717" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="718" spans="1:6">
@@ -20474,7 +20480,7 @@
         <v>704</v>
       </c>
       <c r="E718" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="719" spans="1:6">
@@ -20488,7 +20494,7 @@
         <v>705</v>
       </c>
       <c r="E719" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="720" spans="1:6">
@@ -20502,7 +20508,7 @@
         <v>706</v>
       </c>
       <c r="E720" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="721" spans="1:5">
@@ -20516,7 +20522,7 @@
         <v>707</v>
       </c>
       <c r="E721" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="722" spans="1:5">
@@ -20530,7 +20536,7 @@
         <v>708</v>
       </c>
       <c r="E722" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="723" spans="1:5">
@@ -20544,7 +20550,7 @@
         <v>709</v>
       </c>
       <c r="E723" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="724" spans="1:5">
@@ -20558,7 +20564,7 @@
         <v>710</v>
       </c>
       <c r="E724" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="725" spans="1:5">
@@ -20572,7 +20578,7 @@
         <v>711</v>
       </c>
       <c r="E725" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="726" spans="1:5">
@@ -20586,7 +20592,7 @@
         <v>712</v>
       </c>
       <c r="E726" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="727" spans="1:5">
@@ -20600,7 +20606,7 @@
         <v>713</v>
       </c>
       <c r="E727" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="728" spans="1:5">
@@ -20617,7 +20623,7 @@
         <v>714</v>
       </c>
       <c r="E728" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="729" spans="1:5">
@@ -20634,7 +20640,7 @@
         <v>715</v>
       </c>
       <c r="E729" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -20651,7 +20657,7 @@
         <v>716</v>
       </c>
       <c r="E730" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="731" spans="1:5">
@@ -20668,7 +20674,7 @@
         <v>717</v>
       </c>
       <c r="E731" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="732" spans="1:5">
@@ -20685,7 +20691,7 @@
         <v>718</v>
       </c>
       <c r="E732" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="733" spans="1:5">
@@ -20702,7 +20708,7 @@
         <v>719</v>
       </c>
       <c r="E733" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="734" spans="1:5">
@@ -20719,7 +20725,7 @@
         <v>720</v>
       </c>
       <c r="E734" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="735" spans="1:5">
@@ -20736,7 +20742,7 @@
         <v>721</v>
       </c>
       <c r="E735" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="736" spans="1:5">
@@ -20753,7 +20759,7 @@
         <v>722</v>
       </c>
       <c r="E736" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="737" spans="1:5">
@@ -20770,7 +20776,7 @@
         <v>723</v>
       </c>
       <c r="E737" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="738" spans="1:5">
@@ -20787,7 +20793,7 @@
         <v>724</v>
       </c>
       <c r="E738" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="739" spans="1:5">
@@ -20804,7 +20810,7 @@
         <v>725</v>
       </c>
       <c r="E739" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="740" spans="1:5">
@@ -20821,7 +20827,7 @@
         <v>411</v>
       </c>
       <c r="E740" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="741" spans="1:5">
@@ -20838,7 +20844,7 @@
         <v>726</v>
       </c>
       <c r="E741" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="742" spans="1:5">
@@ -20855,7 +20861,7 @@
         <v>727</v>
       </c>
       <c r="E742" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="743" spans="1:5">
@@ -20872,7 +20878,7 @@
         <v>728</v>
       </c>
       <c r="E743" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="744" spans="1:5">
@@ -20889,7 +20895,7 @@
         <v>729</v>
       </c>
       <c r="E744" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="745" spans="1:5">
@@ -20906,7 +20912,7 @@
         <v>730</v>
       </c>
       <c r="E745" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="746" spans="1:5">
@@ -20923,7 +20929,7 @@
         <v>731</v>
       </c>
       <c r="E746" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="747" spans="1:5">
@@ -20940,7 +20946,7 @@
         <v>411</v>
       </c>
       <c r="E747" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="748" spans="1:5">
@@ -21083,7 +21089,7 @@
         <v>739</v>
       </c>
       <c r="E757" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="758" spans="1:6">
@@ -21100,10 +21106,10 @@
         <v>740</v>
       </c>
       <c r="E758" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="F758" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="759" spans="1:6">
@@ -21120,7 +21126,7 @@
         <v>741</v>
       </c>
       <c r="E759" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="760" spans="1:6">
@@ -21137,7 +21143,7 @@
         <v>742</v>
       </c>
       <c r="E760" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="761" spans="1:6">
@@ -21154,7 +21160,7 @@
         <v>743</v>
       </c>
       <c r="E761" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="762" spans="1:6">
@@ -21171,7 +21177,7 @@
         <v>744</v>
       </c>
       <c r="E762" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="763" spans="1:6">
@@ -21202,7 +21208,7 @@
         <v>745</v>
       </c>
       <c r="E764" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="765" spans="1:6">
@@ -21219,7 +21225,7 @@
         <v>746</v>
       </c>
       <c r="E765" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="766" spans="1:6">
@@ -21236,7 +21242,7 @@
         <v>747</v>
       </c>
       <c r="E766" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="767" spans="1:6">
@@ -21253,7 +21259,7 @@
         <v>748</v>
       </c>
       <c r="E767" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="768" spans="1:6">
@@ -21270,7 +21276,7 @@
         <v>749</v>
       </c>
       <c r="E768" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="769" spans="1:5">
@@ -21287,7 +21293,7 @@
         <v>750</v>
       </c>
       <c r="E769" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="770" spans="1:5">
@@ -21304,7 +21310,7 @@
         <v>751</v>
       </c>
       <c r="E770" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="771" spans="1:5">
@@ -21321,7 +21327,7 @@
         <v>752</v>
       </c>
       <c r="E771" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="772" spans="1:5">
@@ -21338,7 +21344,7 @@
         <v>753</v>
       </c>
       <c r="E772" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="773" spans="1:5">
@@ -21355,7 +21361,7 @@
         <v>754</v>
       </c>
       <c r="E773" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="774" spans="1:5">
@@ -21372,7 +21378,7 @@
         <v>755</v>
       </c>
       <c r="E774" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="775" spans="1:5">
@@ -21389,7 +21395,7 @@
         <v>756</v>
       </c>
       <c r="E775" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="776" spans="1:5">
@@ -21406,7 +21412,7 @@
         <v>757</v>
       </c>
       <c r="E776" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="777" spans="1:5">
@@ -21423,7 +21429,7 @@
         <v>758</v>
       </c>
       <c r="E777" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="778" spans="1:5">
@@ -21440,7 +21446,7 @@
         <v>759</v>
       </c>
       <c r="E778" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="779" spans="1:5">
@@ -21457,7 +21463,7 @@
         <v>760</v>
       </c>
       <c r="E779" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="780" spans="1:5">
@@ -21474,7 +21480,7 @@
         <v>761</v>
       </c>
       <c r="E780" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="781" spans="1:5">
@@ -21491,7 +21497,7 @@
         <v>762</v>
       </c>
       <c r="E781" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="782" spans="1:5">
@@ -21508,7 +21514,7 @@
         <v>763</v>
       </c>
       <c r="E782" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="783" spans="1:5">
@@ -21525,7 +21531,7 @@
         <v>764</v>
       </c>
       <c r="E783" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="784" spans="1:5">
@@ -21542,7 +21548,7 @@
         <v>765</v>
       </c>
       <c r="E784" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="785" spans="1:5">
@@ -21559,7 +21565,7 @@
         <v>766</v>
       </c>
       <c r="E785" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="786" spans="1:5">
@@ -21576,7 +21582,7 @@
         <v>767</v>
       </c>
       <c r="E786" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="787" spans="1:5">
@@ -21593,7 +21599,7 @@
         <v>768</v>
       </c>
       <c r="E787" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="788" spans="1:5">
@@ -21621,7 +21627,7 @@
         <v>769</v>
       </c>
       <c r="E789" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="790" spans="1:5">
@@ -21635,7 +21641,7 @@
         <v>769</v>
       </c>
       <c r="E790" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="791" spans="1:5">
@@ -21649,7 +21655,7 @@
         <v>769</v>
       </c>
       <c r="E791" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="792" spans="1:5">
@@ -21663,7 +21669,7 @@
         <v>769</v>
       </c>
       <c r="E792" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="793" spans="1:5">
@@ -21677,7 +21683,7 @@
         <v>769</v>
       </c>
       <c r="E793" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="794" spans="1:5">
@@ -21694,7 +21700,7 @@
         <v>411</v>
       </c>
       <c r="E794" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="795" spans="1:5">
@@ -21711,7 +21717,7 @@
         <v>770</v>
       </c>
       <c r="E795" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="796" spans="1:5">
@@ -21728,7 +21734,7 @@
         <v>771</v>
       </c>
       <c r="E796" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="797" spans="1:5">
@@ -21745,7 +21751,7 @@
         <v>772</v>
       </c>
       <c r="E797" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="798" spans="1:5">
@@ -21762,7 +21768,7 @@
         <v>15</v>
       </c>
       <c r="E798" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="799" spans="1:5">
@@ -21779,7 +21785,7 @@
         <v>773</v>
       </c>
       <c r="E799" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="800" spans="1:5">
@@ -21807,7 +21813,7 @@
         <v>774</v>
       </c>
       <c r="E801" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="802" spans="1:5">
@@ -21821,7 +21827,7 @@
         <v>775</v>
       </c>
       <c r="E802" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="803" spans="1:5">
@@ -21835,7 +21841,7 @@
         <v>776</v>
       </c>
       <c r="E803" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="804" spans="1:5">
@@ -21866,7 +21872,7 @@
         <v>777</v>
       </c>
       <c r="E805" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="806" spans="1:5">
@@ -21883,7 +21889,7 @@
         <v>778</v>
       </c>
       <c r="E806" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="807" spans="1:5">
@@ -21900,7 +21906,7 @@
         <v>779</v>
       </c>
       <c r="E807" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="808" spans="1:5">
@@ -21917,7 +21923,7 @@
         <v>780</v>
       </c>
       <c r="E808" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="809" spans="1:5">
@@ -21948,7 +21954,7 @@
         <v>781</v>
       </c>
       <c r="E810" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="811" spans="1:5">
@@ -21965,7 +21971,7 @@
         <v>782</v>
       </c>
       <c r="E811" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="812" spans="1:5">
@@ -21982,7 +21988,7 @@
         <v>783</v>
       </c>
       <c r="E812" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="813" spans="1:5">
@@ -21999,7 +22005,7 @@
         <v>784</v>
       </c>
       <c r="E813" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="814" spans="1:5">
@@ -22016,7 +22022,7 @@
         <v>785</v>
       </c>
       <c r="E814" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="815" spans="1:5">
@@ -22033,7 +22039,7 @@
         <v>786</v>
       </c>
       <c r="E815" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="816" spans="1:5">
@@ -22050,7 +22056,7 @@
         <v>411</v>
       </c>
       <c r="E816" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="817" spans="1:6">
@@ -22067,7 +22073,7 @@
         <v>787</v>
       </c>
       <c r="E817" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="818" spans="1:6">
@@ -22084,7 +22090,7 @@
         <v>788</v>
       </c>
       <c r="E818" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="819" spans="1:6">
@@ -22101,7 +22107,7 @@
         <v>789</v>
       </c>
       <c r="E819" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="820" spans="1:6">
@@ -22132,10 +22138,10 @@
         <v>84</v>
       </c>
       <c r="E821" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="F821" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="822" spans="1:6">
@@ -22149,7 +22155,7 @@
         <v>791</v>
       </c>
       <c r="E822" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="823" spans="1:6">
@@ -22163,7 +22169,7 @@
         <v>792</v>
       </c>
       <c r="E823" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="824" spans="1:6">
@@ -22177,7 +22183,7 @@
         <v>793</v>
       </c>
       <c r="E824" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="825" spans="1:6">
@@ -22191,7 +22197,7 @@
         <v>794</v>
       </c>
       <c r="E825" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="826" spans="1:6">
@@ -22205,7 +22211,7 @@
         <v>795</v>
       </c>
       <c r="E826" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="827" spans="1:6">
@@ -22219,7 +22225,7 @@
         <v>796</v>
       </c>
       <c r="E827" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="828" spans="1:6">
@@ -22233,7 +22239,7 @@
         <v>797</v>
       </c>
       <c r="E828" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="829" spans="1:6">
@@ -22247,7 +22253,7 @@
         <v>798</v>
       </c>
       <c r="E829" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="830" spans="1:6">
@@ -22261,7 +22267,7 @@
         <v>799</v>
       </c>
       <c r="E830" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="831" spans="1:6">
@@ -22275,7 +22281,7 @@
         <v>800</v>
       </c>
       <c r="E831" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="832" spans="1:6">
@@ -22377,7 +22383,7 @@
         <v>442</v>
       </c>
       <c r="E840" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="841" spans="2:5">
@@ -22435,7 +22441,7 @@
         <v>801</v>
       </c>
       <c r="E845" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="846" spans="2:5">
@@ -22449,7 +22455,7 @@
         <v>802</v>
       </c>
       <c r="E846" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="847" spans="2:5">
@@ -22474,7 +22480,7 @@
         <v>440</v>
       </c>
       <c r="E848" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="849" spans="1:5">
@@ -22510,7 +22516,7 @@
         <v>448</v>
       </c>
       <c r="E851" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="852" spans="1:5">
@@ -22535,7 +22541,7 @@
         <v>803</v>
       </c>
       <c r="E853" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="854" spans="1:5">
@@ -22549,7 +22555,7 @@
         <v>439</v>
       </c>
       <c r="E854" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="855" spans="1:5">
@@ -22585,7 +22591,7 @@
         <v>804</v>
       </c>
       <c r="E857" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="858" spans="1:5">
@@ -22599,7 +22605,7 @@
         <v>805</v>
       </c>
       <c r="E858" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="859" spans="1:5">
@@ -22646,7 +22652,7 @@
         <v>441</v>
       </c>
       <c r="E862" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="863" spans="1:5">
@@ -22663,7 +22669,15 @@
         <v>411</v>
       </c>
       <c r="E863" t="s">
-        <v>1507</v>
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="864" spans="1:5">
+      <c r="D864" t="s">
+        <v>806</v>
+      </c>
+      <c r="E864" t="s">
+        <v>1509</v>
       </c>
     </row>
   </sheetData>
